--- a/wwwroot/template/HistoryQuote.xlsx
+++ b/wwwroot/template/HistoryQuote.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662613DC-D303-41E7-A717-7DE8A04B593D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8769F39-793F-4CFA-932C-4AFC1943D9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
-    <sheet name="フォーム説明" sheetId="7" r:id="rId2"/>
-    <sheet name="Master" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="フォーム説明" sheetId="7" state="hidden" r:id="rId2"/>
+    <sheet name="Input form (ex)" sheetId="8" r:id="rId3"/>
+    <sheet name="Master" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">フォーム説明!$B$1:$H$35</definedName>
   </definedNames>
@@ -680,7 +684,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="525">
   <si>
     <t>No</t>
   </si>
@@ -2459,6 +2463,70 @@
   <si>
     <t>Pallet</t>
   </si>
+  <si>
+    <t>Phải điền</t>
+  </si>
+  <si>
+    <t>Không cần điền</t>
+  </si>
+  <si>
+    <t>Có nhu cầu thì điền</t>
+  </si>
+  <si>
+    <t>Đọc lại điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mã cũ (mã đã có trong file master). </t>
+  </si>
+  <si>
+    <t>Lí do xin báo giá
+Reason for quotation request</t>
+  </si>
+  <si>
+    <t>O00000863</t>
+  </si>
+  <si>
+    <t>Nếu là mã ngoài danh mục có thiết kế: Phải đính kèm</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>O00000864</t>
+  </si>
+  <si>
+    <t>Nếu là mã tiêu chuẩn: Không cần</t>
+  </si>
+  <si>
+    <t>O00000865</t>
+  </si>
+  <si>
+    <t>Nếu là sữar chữa/bảo dưỡng/thi công...: cần copy link format PL12 hoặc PL13</t>
+  </si>
+  <si>
+    <t>2. Mã mới : Chưa mua bao giờ</t>
+  </si>
+  <si>
+    <t>cái/chiếc</t>
+  </si>
+  <si>
+    <t>Up ngoài phần lựa chọn &gt;&gt; báo lỗi ko up được</t>
+  </si>
+  <si>
+    <t>Không được để trống</t>
+  </si>
+  <si>
+    <t>Phải điền, với hàng dịch vụ ghi "-"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hệ thống báo lỗi file nếu PIC cố tình thêm NCC ko có trong MAP tương ứng chủng loại (VD: chủng loại A chỉ có 2 vendor , PIC cố tình add thêm vendor 3 &gt;&gt; báo lỗi ko cho up) </t>
+  </si>
+  <si>
+    <t>phải có trong MAP</t>
+  </si>
+  <si>
+    <t>Điền tay mà điền sai vendor code ko có trong MAP &gt;&gt; báo lỗi ko cho up</t>
+  </si>
 </sst>
 </file>
 
@@ -2467,7 +2535,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2567,8 +2635,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2593,8 +2689,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2689,11 +2809,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2783,14 +2970,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2810,27 +3022,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2843,14 +3034,127 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2873,6 +3177,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Form blank"/>
+      <sheetName val="フォーム説明"/>
+      <sheetName val="Master"/>
+      <sheetName val="Sheet4"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3298,19 +3624,19 @@
       <c r="AF2" s="9"/>
     </row>
     <row r="3" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>382</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="18"/>
       <c r="M3" s="18"/>
       <c r="N3" s="18"/>
@@ -3372,15 +3698,15 @@
       <c r="N4" s="25">
         <v>12</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="45">
         <f>N4+1</f>
         <v>13</v>
       </c>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="38"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="47"/>
       <c r="U4" s="24">
         <v>14</v>
       </c>
@@ -3440,120 +3766,120 @@
       </c>
     </row>
     <row r="5" spans="1:36" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="39" t="s">
         <v>390</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="39" t="s">
         <v>391</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="39" t="s">
         <v>333</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="39" t="s">
         <v>337</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="I5" s="39" t="s">
         <v>338</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="L5" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="39" t="s">
         <v>342</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="O5" s="39" t="s">
+      <c r="O5" s="48" t="s">
         <v>349</v>
       </c>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="41"/>
-      <c r="U5" s="33" t="s">
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="39" t="s">
         <v>353</v>
       </c>
-      <c r="V5" s="33" t="s">
+      <c r="V5" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="W5" s="33" t="s">
+      <c r="W5" s="39" t="s">
         <v>350</v>
       </c>
-      <c r="X5" s="33" t="s">
+      <c r="X5" s="39" t="s">
         <v>351</v>
       </c>
-      <c r="Y5" s="33" t="s">
+      <c r="Y5" s="39" t="s">
         <v>355</v>
       </c>
-      <c r="Z5" s="33" t="s">
+      <c r="Z5" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="AA5" s="33" t="s">
+      <c r="AA5" s="39" t="s">
         <v>357</v>
       </c>
-      <c r="AB5" s="33" t="s">
+      <c r="AB5" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="AC5" s="33" t="s">
+      <c r="AC5" s="39" t="s">
         <v>359</v>
       </c>
-      <c r="AD5" s="33" t="s">
+      <c r="AD5" s="39" t="s">
         <v>360</v>
       </c>
-      <c r="AE5" s="33" t="s">
+      <c r="AE5" s="39" t="s">
         <v>361</v>
       </c>
-      <c r="AF5" s="33" t="s">
+      <c r="AF5" s="39" t="s">
         <v>362</v>
       </c>
-      <c r="AG5" s="35" t="s">
+      <c r="AG5" s="38" t="s">
         <v>363</v>
       </c>
-      <c r="AH5" s="35" t="s">
+      <c r="AH5" s="38" t="s">
         <v>364</v>
       </c>
-      <c r="AI5" s="33" t="s">
+      <c r="AI5" s="39" t="s">
         <v>388</v>
       </c>
-      <c r="AJ5" s="35" t="s">
+      <c r="AJ5" s="38" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
       <c r="O6" s="19" t="s">
         <v>344</v>
       </c>
@@ -3572,22 +3898,22 @@
       <c r="T6" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="W6" s="34"/>
-      <c r="X6" s="34"/>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="34"/>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="34"/>
-      <c r="AC6" s="34"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="34"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="35"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="34"/>
-      <c r="AJ6" s="35"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="40"/>
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="38"/>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -30471,6 +30797,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AD5:AD6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
     <mergeCell ref="U5:U6"/>
@@ -30487,23 +30830,6 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="Z5:Z6"/>
     <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="AE5:AE6"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AD5:AD6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC7:AC566" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -30566,11 +30892,11 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="20" t="s">
         <v>329</v>
       </c>
@@ -30580,11 +30906,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="53" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="20" t="s">
         <v>329</v>
       </c>
@@ -30599,10 +30925,10 @@
       <c r="B4" s="28">
         <v>1</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="48"/>
+      <c r="D4" s="57"/>
       <c r="E4" s="20" t="s">
         <v>324</v>
       </c>
@@ -30615,10 +30941,10 @@
       <c r="B5" s="28">
         <v>2</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="51" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="50"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="20" t="s">
         <v>324</v>
       </c>
@@ -30630,10 +30956,10 @@
       <c r="B6" s="28">
         <v>3</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="51" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="50"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="20" t="s">
         <v>329</v>
       </c>
@@ -30648,10 +30974,10 @@
       <c r="B7" s="28">
         <v>4</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="51" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="50"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="20" t="s">
         <v>329</v>
       </c>
@@ -30666,10 +30992,10 @@
       <c r="B8" s="28">
         <v>5</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="50"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="20" t="s">
         <v>326</v>
       </c>
@@ -30684,10 +31010,10 @@
       <c r="B9" s="28">
         <v>6</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="51" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="50"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="20" t="s">
         <v>324</v>
       </c>
@@ -30702,10 +31028,10 @@
       <c r="B10" s="28">
         <v>7</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="51" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="50"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="20" t="s">
         <v>329</v>
       </c>
@@ -30720,10 +31046,10 @@
       <c r="B11" s="28">
         <v>8</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="50"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="20" t="s">
         <v>329</v>
       </c>
@@ -30738,10 +31064,10 @@
       <c r="B12" s="28">
         <v>9</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="51" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="50"/>
+      <c r="D12" s="52"/>
       <c r="E12" s="20" t="s">
         <v>329</v>
       </c>
@@ -30754,10 +31080,10 @@
       <c r="B13" s="28">
         <v>10</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="51" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="50"/>
+      <c r="D13" s="52"/>
       <c r="E13" s="20" t="s">
         <v>324</v>
       </c>
@@ -30770,10 +31096,10 @@
       <c r="B14" s="28">
         <v>11</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="D14" s="50"/>
+      <c r="D14" s="52"/>
       <c r="E14" s="20" t="s">
         <v>324</v>
       </c>
@@ -30786,10 +31112,10 @@
       <c r="B15" s="28">
         <v>12</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="50"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="20" t="s">
         <v>329</v>
       </c>
@@ -30801,11 +31127,11 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="52">
+      <c r="B16" s="54">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="55" t="s">
         <v>349</v>
       </c>
       <c r="D16" s="29" t="s">
@@ -30822,8 +31148,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="52"/>
-      <c r="C17" s="46"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="29" t="s">
         <v>345</v>
       </c>
@@ -30838,8 +31164,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="52"/>
-      <c r="C18" s="46"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="29" t="s">
         <v>346</v>
       </c>
@@ -30854,8 +31180,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="52"/>
-      <c r="C19" s="46"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="29" t="s">
         <v>347</v>
       </c>
@@ -30870,8 +31196,8 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="52"/>
-      <c r="C20" s="46"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="29" t="s">
         <v>348</v>
       </c>
@@ -30886,8 +31212,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="52"/>
-      <c r="C21" s="46"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
       <c r="D21" s="29" t="s">
         <v>352</v>
       </c>
@@ -30905,10 +31231,10 @@
       <c r="B22" s="30">
         <v>14</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="50"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="20" t="s">
         <v>326</v>
       </c>
@@ -30924,10 +31250,10 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="51" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="50"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="20" t="s">
         <v>326</v>
       </c>
@@ -30943,10 +31269,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="51" t="s">
         <v>350</v>
       </c>
-      <c r="D24" s="50"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="20" t="s">
         <v>326</v>
       </c>
@@ -30962,10 +31288,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="51" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="50"/>
+      <c r="D25" s="52"/>
       <c r="E25" s="20" t="s">
         <v>326</v>
       </c>
@@ -30981,10 +31307,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="51" t="s">
         <v>355</v>
       </c>
-      <c r="D26" s="50"/>
+      <c r="D26" s="52"/>
       <c r="E26" s="20" t="s">
         <v>331</v>
       </c>
@@ -31000,10 +31326,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="51" t="s">
         <v>356</v>
       </c>
-      <c r="D27" s="50"/>
+      <c r="D27" s="52"/>
       <c r="E27" s="20" t="s">
         <v>329</v>
       </c>
@@ -31019,10 +31345,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="D28" s="50"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="20" t="s">
         <v>329</v>
       </c>
@@ -31038,10 +31364,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="51" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="50"/>
+      <c r="D29" s="52"/>
       <c r="E29" s="20" t="s">
         <v>329</v>
       </c>
@@ -31057,10 +31383,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="D30" s="50"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="20" t="s">
         <v>324</v>
       </c>
@@ -31076,10 +31402,10 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="51" t="s">
         <v>360</v>
       </c>
-      <c r="D31" s="50"/>
+      <c r="D31" s="52"/>
       <c r="E31" s="20" t="s">
         <v>324</v>
       </c>
@@ -31095,10 +31421,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="51" t="s">
         <v>361</v>
       </c>
-      <c r="D32" s="50"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="20" t="s">
         <v>324</v>
       </c>
@@ -31112,10 +31438,10 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="51" t="s">
         <v>362</v>
       </c>
-      <c r="D33" s="50"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="20" t="s">
         <v>324</v>
       </c>
@@ -31131,10 +31457,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C34" s="55" t="s">
         <v>363</v>
       </c>
-      <c r="D34" s="46"/>
+      <c r="D34" s="55"/>
       <c r="E34" s="20" t="s">
         <v>326</v>
       </c>
@@ -31150,10 +31476,10 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="46" t="s">
+      <c r="C35" s="55" t="s">
         <v>364</v>
       </c>
-      <c r="D35" s="46"/>
+      <c r="D35" s="55"/>
       <c r="E35" s="20" t="s">
         <v>326</v>
       </c>
@@ -31167,20 +31493,6 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -31197,6 +31509,20 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -31204,6 +31530,1076 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBCE33F-019A-480D-A309-E4ED2C08EDE5}">
+  <dimension ref="A1:AG21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="52.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="59"/>
+      <c r="B1" s="60" t="s">
+        <v>504</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1" s="63" t="s">
+        <v>506</v>
+      </c>
+      <c r="F1" s="64" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="59"/>
+      <c r="E2" s="59"/>
+    </row>
+    <row r="3" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="65" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="66">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25">
+        <v>2</v>
+      </c>
+      <c r="C4" s="25">
+        <v>3</v>
+      </c>
+      <c r="D4" s="25">
+        <v>4</v>
+      </c>
+      <c r="E4" s="25">
+        <v>5</v>
+      </c>
+      <c r="F4" s="25">
+        <v>6</v>
+      </c>
+      <c r="G4" s="25">
+        <v>7</v>
+      </c>
+      <c r="H4" s="25">
+        <v>8</v>
+      </c>
+      <c r="I4" s="25">
+        <v>9</v>
+      </c>
+      <c r="J4" s="25">
+        <v>10</v>
+      </c>
+      <c r="K4" s="25">
+        <v>11</v>
+      </c>
+      <c r="L4" s="25">
+        <v>12</v>
+      </c>
+      <c r="M4" s="45">
+        <f>L4+1</f>
+        <v>13</v>
+      </c>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="34">
+        <v>14</v>
+      </c>
+      <c r="T4" s="25">
+        <f>S4+1</f>
+        <v>15</v>
+      </c>
+      <c r="U4" s="25">
+        <f t="shared" ref="U4:AF4" si="0">T4+1</f>
+        <v>16</v>
+      </c>
+      <c r="V4" s="25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="W4" s="25">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="X4" s="25">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="Y4" s="25">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z4" s="25">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="AA4" s="25">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="AB4" s="25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="AC4" s="25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AD4" s="25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="AE4" s="25">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="AF4" s="33">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="AG4" s="25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="H5" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="I5" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="J5" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="K5" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="L5" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="M5" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="T5" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="U5" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="V5" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="W5" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="X5" s="69" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y5" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="Z5" s="69" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA5" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB5" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="AC5" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="AD5" s="69" t="s">
+        <v>362</v>
+      </c>
+      <c r="AE5" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF5" s="70" t="s">
+        <v>364</v>
+      </c>
+      <c r="AG5" s="73" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="74"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="76" t="s">
+        <v>344</v>
+      </c>
+      <c r="N6" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="O6" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="P6" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q6" s="76" t="s">
+        <v>348</v>
+      </c>
+      <c r="R6" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="75"/>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="70"/>
+      <c r="AG6" s="73"/>
+    </row>
+    <row r="7" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="77">
+        <v>1</v>
+      </c>
+      <c r="B7" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C7" s="79" t="e">
+        <f>VLOOKUP(B7,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="78" t="s">
+        <v>510</v>
+      </c>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81" t="str">
+        <f>L7&amp;"có hình dáng dạng "&amp;M7&amp;" chất liệu "&amp;N7&amp;" thành phần hóa chất: "&amp;O7&amp;" có kích thước "&amp;P7&amp;" dùng để "&amp;R7&amp;" cho "&amp;Q7</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I7" s="81"/>
+      <c r="J7" s="78">
+        <v>10</v>
+      </c>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="83"/>
+      <c r="W7" s="84" t="s">
+        <v>511</v>
+      </c>
+      <c r="X7" s="81"/>
+      <c r="Y7" s="81"/>
+      <c r="Z7" s="81"/>
+      <c r="AA7" s="85" t="s">
+        <v>512</v>
+      </c>
+      <c r="AB7" s="80"/>
+      <c r="AC7" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD7" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE7" s="80"/>
+      <c r="AF7" s="87"/>
+      <c r="AG7" s="80"/>
+    </row>
+    <row r="8" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="77">
+        <v>2</v>
+      </c>
+      <c r="B8" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C8" s="79" t="e">
+        <f>VLOOKUP(B8,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D8" s="79"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="78" t="s">
+        <v>513</v>
+      </c>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81" t="str">
+        <f t="shared" ref="H8:H9" si="1">L8&amp;"có hình dáng dạng "&amp;M8&amp;" chất liệu "&amp;N8&amp;" thành phần hóa chất: "&amp;O8&amp;" có kích thước "&amp;P8&amp;" dùng để "&amp;R8&amp;" cho "&amp;Q8</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I8" s="81"/>
+      <c r="J8" s="78">
+        <v>10</v>
+      </c>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="82"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="84" t="s">
+        <v>514</v>
+      </c>
+      <c r="X8" s="81"/>
+      <c r="Y8" s="81"/>
+      <c r="Z8" s="81"/>
+      <c r="AA8" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD8" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE8" s="80"/>
+      <c r="AF8" s="87"/>
+      <c r="AG8" s="80"/>
+    </row>
+    <row r="9" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="77">
+        <v>3</v>
+      </c>
+      <c r="B9" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C9" s="79" t="e">
+        <f>VLOOKUP(B9,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D9" s="79"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I9" s="81"/>
+      <c r="J9" s="78">
+        <v>10</v>
+      </c>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="84" t="s">
+        <v>516</v>
+      </c>
+      <c r="X9" s="81"/>
+      <c r="Y9" s="81"/>
+      <c r="Z9" s="81"/>
+      <c r="AA9" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD9" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE9" s="80"/>
+      <c r="AF9" s="87"/>
+      <c r="AG9" s="80"/>
+    </row>
+    <row r="10" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H10" s="62" t="str">
+        <f t="shared" ref="H10:H11" si="2">M10&amp;" "&amp;N10&amp;" "&amp;O10&amp;""&amp;P10&amp;" "&amp;Q10&amp;" "&amp;R10</f>
+        <v xml:space="preserve">    </v>
+      </c>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="AA10" s="89"/>
+      <c r="AC10" s="90"/>
+      <c r="AD10" s="90"/>
+    </row>
+    <row r="11" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H11" s="62" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">    </v>
+      </c>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="AA11" s="89"/>
+      <c r="AC11" s="90"/>
+      <c r="AD11" s="90"/>
+    </row>
+    <row r="12" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="65" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="66">
+        <v>1</v>
+      </c>
+      <c r="B13" s="25">
+        <v>2</v>
+      </c>
+      <c r="C13" s="25">
+        <v>3</v>
+      </c>
+      <c r="D13" s="25">
+        <v>4</v>
+      </c>
+      <c r="E13" s="25">
+        <v>5</v>
+      </c>
+      <c r="F13" s="25">
+        <v>6</v>
+      </c>
+      <c r="G13" s="25">
+        <v>7</v>
+      </c>
+      <c r="H13" s="25">
+        <v>8</v>
+      </c>
+      <c r="I13" s="25">
+        <v>9</v>
+      </c>
+      <c r="J13" s="25">
+        <v>10</v>
+      </c>
+      <c r="K13" s="25">
+        <v>11</v>
+      </c>
+      <c r="L13" s="25">
+        <v>12</v>
+      </c>
+      <c r="M13" s="45">
+        <f>L13+1</f>
+        <v>13</v>
+      </c>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="34">
+        <v>14</v>
+      </c>
+      <c r="T13" s="25">
+        <f>S13+1</f>
+        <v>15</v>
+      </c>
+      <c r="U13" s="25">
+        <f t="shared" ref="U13:AF13" si="3">T13+1</f>
+        <v>16</v>
+      </c>
+      <c r="V13" s="25">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="W13" s="25">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="X13" s="25">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="Y13" s="25">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="Z13" s="25">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="AA13" s="25">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="AB13" s="25">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="AC13" s="25">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="AD13" s="25">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="AE13" s="25">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="AF13" s="91">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="AG13" s="25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="D14" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="H14" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="I14" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="J14" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="K14" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="L14" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="M14" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="T14" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="U14" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="V14" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="W14" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="X14" s="69" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y14" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="Z14" s="69" t="s">
+        <v>358</v>
+      </c>
+      <c r="AA14" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="AB14" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="AC14" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="AD14" s="69" t="s">
+        <v>362</v>
+      </c>
+      <c r="AE14" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="AF14" s="92" t="s">
+        <v>364</v>
+      </c>
+      <c r="AG14" s="73" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="74"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="76" t="s">
+        <v>344</v>
+      </c>
+      <c r="N15" s="76" t="s">
+        <v>345</v>
+      </c>
+      <c r="O15" s="76" t="s">
+        <v>346</v>
+      </c>
+      <c r="P15" s="76" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q15" s="76" t="s">
+        <v>348</v>
+      </c>
+      <c r="R15" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="S15" s="75"/>
+      <c r="T15" s="75"/>
+      <c r="U15" s="75"/>
+      <c r="V15" s="75"/>
+      <c r="W15" s="75"/>
+      <c r="X15" s="75"/>
+      <c r="Y15" s="75"/>
+      <c r="Z15" s="75"/>
+      <c r="AA15" s="75"/>
+      <c r="AB15" s="75"/>
+      <c r="AC15" s="75"/>
+      <c r="AD15" s="75"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="92"/>
+      <c r="AG15" s="73"/>
+    </row>
+    <row r="16" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="77">
+        <v>1</v>
+      </c>
+      <c r="B16" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C16" s="79" t="e">
+        <f>VLOOKUP(B16,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="78"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="81" t="str">
+        <f>L16&amp;"có hình dáng dạng "&amp;M16&amp;" chất liệu "&amp;N16&amp;" thành phần hóa chất: "&amp;O16&amp;" có kích thước "&amp;P16&amp;" dùng để "&amp;R16&amp;" cho "&amp;Q16</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78">
+        <v>10</v>
+      </c>
+      <c r="K16" s="78" t="s">
+        <v>518</v>
+      </c>
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="78"/>
+      <c r="R16" s="93"/>
+      <c r="S16" s="83"/>
+      <c r="T16" s="83"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="83"/>
+      <c r="W16" s="84" t="s">
+        <v>511</v>
+      </c>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="81"/>
+      <c r="AA16" s="85" t="s">
+        <v>512</v>
+      </c>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD16" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE16" s="80"/>
+      <c r="AF16" s="94"/>
+      <c r="AG16" s="80"/>
+    </row>
+    <row r="17" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="77">
+        <v>2</v>
+      </c>
+      <c r="B17" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C17" s="79" t="e">
+        <f>VLOOKUP(B17,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="78"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="81" t="str">
+        <f t="shared" ref="H17:H19" si="4">L17&amp;"có hình dáng dạng "&amp;M17&amp;" chất liệu "&amp;N17&amp;" thành phần hóa chất: "&amp;O17&amp;" có kích thước "&amp;P17&amp;" dùng để "&amp;R17&amp;" cho "&amp;Q17</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78">
+        <v>10</v>
+      </c>
+      <c r="K17" s="78" t="s">
+        <v>518</v>
+      </c>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="78"/>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="80"/>
+      <c r="T17" s="80"/>
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="84" t="s">
+        <v>514</v>
+      </c>
+      <c r="X17" s="80"/>
+      <c r="Y17" s="81"/>
+      <c r="Z17" s="81"/>
+      <c r="AA17" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="80"/>
+      <c r="AC17" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD17" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE17" s="80"/>
+      <c r="AF17" s="94"/>
+      <c r="AG17" s="80"/>
+    </row>
+    <row r="18" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="77">
+        <v>3</v>
+      </c>
+      <c r="B18" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C18" s="79" t="e">
+        <f>VLOOKUP(B18,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="78"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I18" s="78"/>
+      <c r="J18" s="78">
+        <v>10</v>
+      </c>
+      <c r="K18" s="78" t="s">
+        <v>518</v>
+      </c>
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
+      <c r="Q18" s="78"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="84" t="s">
+        <v>516</v>
+      </c>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="81"/>
+      <c r="AA18" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="80"/>
+      <c r="AC18" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD18" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE18" s="80"/>
+      <c r="AF18" s="94"/>
+      <c r="AG18" s="80"/>
+    </row>
+    <row r="19" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="77">
+        <v>3</v>
+      </c>
+      <c r="B19" s="78">
+        <v>3110</v>
+      </c>
+      <c r="C19" s="79" t="e">
+        <f>VLOOKUP(B19,[1]Master!D:E,2,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="78"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+      </c>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78">
+        <v>10</v>
+      </c>
+      <c r="K19" s="78" t="s">
+        <v>518</v>
+      </c>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="84" t="s">
+        <v>516</v>
+      </c>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="81"/>
+      <c r="AA19" s="85" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB19" s="80"/>
+      <c r="AC19" s="86">
+        <v>46143</v>
+      </c>
+      <c r="AD19" s="86">
+        <v>46132</v>
+      </c>
+      <c r="AE19" s="80"/>
+      <c r="AF19" s="94"/>
+      <c r="AG19" s="94"/>
+    </row>
+    <row r="20" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="D20" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="K20" s="95" t="s">
+        <v>519</v>
+      </c>
+      <c r="L20" s="95" t="s">
+        <v>520</v>
+      </c>
+      <c r="M20" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="N20" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="O20" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="P20" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q20" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="R20" s="95" t="s">
+        <v>521</v>
+      </c>
+      <c r="Y20" s="95" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="L21" s="95" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y21" s="95" t="s">
+        <v>524</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="58">
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:R14"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="M13:R13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AE5:AE6"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA7:AA11 AA16:AA18" xr:uid="{799C4DBD-0D65-4AB3-8350-D2591EB5B20C}">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7:D11 D16:D18" xr:uid="{8C8F8FE4-B794-4C9D-8476-8FF633844360}">
+      <formula1>"A,E,Ngoài danh mục"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE7:AE11 AE16:AE18" xr:uid="{ACDB70A1-6E6E-47A5-880E-C727DBAC41B0}">
+      <formula1>" ,O"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S10:S11" xr:uid="{C4B52C2D-6078-4188-9E72-E776BAC9E086}">
+      <formula1>",Need (cần)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T11" xr:uid="{8B36196A-D6EA-4297-BF10-62BAA747F927}">
+      <formula1>"CO,CQ,CO&amp;CQ"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDAC048-C2F1-4ABA-B2C8-6CB3150A85B7}">
   <dimension ref="A1:D171"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
@@ -31231,7 +32627,7 @@
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="54" t="s">
+      <c r="D2" s="35" t="s">
         <v>393</v>
       </c>
     </row>
@@ -31242,7 +32638,7 @@
       <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="35" t="s">
         <v>394</v>
       </c>
     </row>
@@ -31253,7 +32649,7 @@
       <c r="B4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="35" t="s">
         <v>395</v>
       </c>
     </row>
@@ -31264,7 +32660,7 @@
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="35" t="s">
         <v>396</v>
       </c>
     </row>
@@ -31275,7 +32671,7 @@
       <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="35" t="s">
         <v>397</v>
       </c>
     </row>
@@ -31286,7 +32682,7 @@
       <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="54" t="s">
+      <c r="D7" s="35" t="s">
         <v>398</v>
       </c>
     </row>
@@ -31297,7 +32693,7 @@
       <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="36" t="s">
         <v>399</v>
       </c>
     </row>
@@ -31308,7 +32704,7 @@
       <c r="B9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="36" t="s">
         <v>400</v>
       </c>
     </row>
@@ -31319,7 +32715,7 @@
       <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="35" t="s">
         <v>401</v>
       </c>
     </row>
@@ -31330,7 +32726,7 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="36" t="s">
         <v>402</v>
       </c>
     </row>
@@ -31341,7 +32737,7 @@
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="35" t="s">
         <v>403</v>
       </c>
     </row>
@@ -31352,7 +32748,7 @@
       <c r="B13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="35" t="s">
         <v>404</v>
       </c>
     </row>
@@ -31363,7 +32759,7 @@
       <c r="B14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="35" t="s">
         <v>405</v>
       </c>
     </row>
@@ -31374,7 +32770,7 @@
       <c r="B15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="35" t="s">
         <v>406</v>
       </c>
     </row>
@@ -31385,7 +32781,7 @@
       <c r="B16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="35" t="s">
         <v>407</v>
       </c>
     </row>
@@ -31396,7 +32792,7 @@
       <c r="B17" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="35" t="s">
         <v>408</v>
       </c>
     </row>
@@ -31407,7 +32803,7 @@
       <c r="B18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="35" t="s">
         <v>409</v>
       </c>
     </row>
@@ -31418,7 +32814,7 @@
       <c r="B19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="36" t="s">
         <v>410</v>
       </c>
     </row>
@@ -31429,7 +32825,7 @@
       <c r="B20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="36" t="s">
         <v>411</v>
       </c>
     </row>
@@ -31440,7 +32836,7 @@
       <c r="B21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="36" t="s">
         <v>412</v>
       </c>
     </row>
@@ -31451,7 +32847,7 @@
       <c r="B22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="35" t="s">
         <v>413</v>
       </c>
     </row>
@@ -31462,7 +32858,7 @@
       <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="36" t="s">
         <v>414</v>
       </c>
     </row>
@@ -31473,7 +32869,7 @@
       <c r="B24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="35" t="s">
         <v>415</v>
       </c>
     </row>
@@ -31484,7 +32880,7 @@
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="36" t="s">
         <v>416</v>
       </c>
     </row>
@@ -31495,7 +32891,7 @@
       <c r="B26" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="36" t="s">
         <v>417</v>
       </c>
     </row>
@@ -31506,7 +32902,7 @@
       <c r="B27" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="D27" s="35" t="s">
         <v>418</v>
       </c>
     </row>
@@ -31517,7 +32913,7 @@
       <c r="B28" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="54" t="s">
+      <c r="D28" s="35" t="s">
         <v>419</v>
       </c>
     </row>
@@ -31528,7 +32924,7 @@
       <c r="B29" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="36" t="s">
         <v>420</v>
       </c>
     </row>
@@ -31539,7 +32935,7 @@
       <c r="B30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="55" t="s">
+      <c r="D30" s="36" t="s">
         <v>421</v>
       </c>
     </row>
@@ -31550,7 +32946,7 @@
       <c r="B31" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="35" t="s">
         <v>422</v>
       </c>
     </row>
@@ -31561,7 +32957,7 @@
       <c r="B32" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="35" t="s">
         <v>423</v>
       </c>
     </row>
@@ -31572,7 +32968,7 @@
       <c r="B33" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="35" t="s">
         <v>424</v>
       </c>
     </row>
@@ -31583,7 +32979,7 @@
       <c r="B34" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="35" t="s">
         <v>425</v>
       </c>
     </row>
@@ -31594,7 +32990,7 @@
       <c r="B35" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="54" t="s">
+      <c r="D35" s="35" t="s">
         <v>426</v>
       </c>
     </row>
@@ -31605,7 +33001,7 @@
       <c r="B36" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="35" t="s">
         <v>427</v>
       </c>
     </row>
@@ -31616,7 +33012,7 @@
       <c r="B37" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="54" t="s">
+      <c r="D37" s="35" t="s">
         <v>428</v>
       </c>
     </row>
@@ -31627,7 +33023,7 @@
       <c r="B38" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="55" t="s">
+      <c r="D38" s="36" t="s">
         <v>429</v>
       </c>
     </row>
@@ -31638,7 +33034,7 @@
       <c r="B39" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D39" s="35" t="s">
         <v>430</v>
       </c>
     </row>
@@ -31649,7 +33045,7 @@
       <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D40" s="35" t="s">
         <v>431</v>
       </c>
     </row>
@@ -31660,7 +33056,7 @@
       <c r="B41" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="54" t="s">
+      <c r="D41" s="35" t="s">
         <v>432</v>
       </c>
     </row>
@@ -31671,7 +33067,7 @@
       <c r="B42" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="54" t="s">
+      <c r="D42" s="35" t="s">
         <v>433</v>
       </c>
     </row>
@@ -31682,7 +33078,7 @@
       <c r="B43" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="54" t="s">
+      <c r="D43" s="35" t="s">
         <v>434</v>
       </c>
     </row>
@@ -31693,7 +33089,7 @@
       <c r="B44" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="54" t="s">
+      <c r="D44" s="35" t="s">
         <v>435</v>
       </c>
     </row>
@@ -31704,7 +33100,7 @@
       <c r="B45" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="35" t="s">
         <v>436</v>
       </c>
     </row>
@@ -31715,7 +33111,7 @@
       <c r="B46" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="54" t="s">
+      <c r="D46" s="35" t="s">
         <v>437</v>
       </c>
     </row>
@@ -31726,7 +33122,7 @@
       <c r="B47" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="54" t="s">
+      <c r="D47" s="35" t="s">
         <v>438</v>
       </c>
     </row>
@@ -31737,7 +33133,7 @@
       <c r="B48" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="54" t="s">
+      <c r="D48" s="35" t="s">
         <v>439</v>
       </c>
     </row>
@@ -31748,7 +33144,7 @@
       <c r="B49" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="54" t="s">
+      <c r="D49" s="35" t="s">
         <v>440</v>
       </c>
     </row>
@@ -31759,7 +33155,7 @@
       <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="D50" s="35" t="s">
         <v>441</v>
       </c>
     </row>
@@ -31770,7 +33166,7 @@
       <c r="B51" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="54" t="s">
+      <c r="D51" s="35" t="s">
         <v>442</v>
       </c>
     </row>
@@ -31781,7 +33177,7 @@
       <c r="B52" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="54" t="s">
+      <c r="D52" s="35" t="s">
         <v>443</v>
       </c>
     </row>
@@ -31792,7 +33188,7 @@
       <c r="B53" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="54" t="s">
+      <c r="D53" s="35" t="s">
         <v>444</v>
       </c>
     </row>
@@ -31803,7 +33199,7 @@
       <c r="B54" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="55" t="s">
+      <c r="D54" s="36" t="s">
         <v>445</v>
       </c>
     </row>
@@ -31814,7 +33210,7 @@
       <c r="B55" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="55" t="s">
+      <c r="D55" s="36" t="s">
         <v>446</v>
       </c>
     </row>
@@ -31825,7 +33221,7 @@
       <c r="B56" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="55" t="s">
+      <c r="D56" s="36" t="s">
         <v>447</v>
       </c>
     </row>
@@ -31836,7 +33232,7 @@
       <c r="B57" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="54" t="s">
+      <c r="D57" s="35" t="s">
         <v>448</v>
       </c>
     </row>
@@ -31847,7 +33243,7 @@
       <c r="B58" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="54" t="s">
+      <c r="D58" s="35" t="s">
         <v>449</v>
       </c>
     </row>
@@ -31858,7 +33254,7 @@
       <c r="B59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D59" s="55" t="s">
+      <c r="D59" s="36" t="s">
         <v>450</v>
       </c>
     </row>
@@ -31869,7 +33265,7 @@
       <c r="B60" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D60" s="54" t="s">
+      <c r="D60" s="35" t="s">
         <v>451</v>
       </c>
     </row>
@@ -31880,7 +33276,7 @@
       <c r="B61" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="54" t="s">
+      <c r="D61" s="35" t="s">
         <v>452</v>
       </c>
     </row>
@@ -31891,7 +33287,7 @@
       <c r="B62" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D62" s="54" t="s">
+      <c r="D62" s="35" t="s">
         <v>453</v>
       </c>
     </row>
@@ -31902,7 +33298,7 @@
       <c r="B63" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D63" s="54" t="s">
+      <c r="D63" s="35" t="s">
         <v>454</v>
       </c>
     </row>
@@ -31913,7 +33309,7 @@
       <c r="B64" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="54" t="s">
+      <c r="D64" s="35" t="s">
         <v>455</v>
       </c>
     </row>
@@ -31924,7 +33320,7 @@
       <c r="B65" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D65" s="54" t="s">
+      <c r="D65" s="35" t="s">
         <v>456</v>
       </c>
     </row>
@@ -31935,7 +33331,7 @@
       <c r="B66" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="54" t="s">
+      <c r="D66" s="35" t="s">
         <v>457</v>
       </c>
     </row>
@@ -31946,7 +33342,7 @@
       <c r="B67" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="55" t="s">
+      <c r="D67" s="36" t="s">
         <v>458</v>
       </c>
     </row>
@@ -31957,7 +33353,7 @@
       <c r="B68" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="55" t="s">
+      <c r="D68" s="36" t="s">
         <v>459</v>
       </c>
     </row>
@@ -31968,7 +33364,7 @@
       <c r="B69" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="54" t="s">
+      <c r="D69" s="35" t="s">
         <v>460</v>
       </c>
     </row>
@@ -31979,7 +33375,7 @@
       <c r="B70" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D70" s="55" t="s">
+      <c r="D70" s="36" t="s">
         <v>461</v>
       </c>
     </row>
@@ -31990,7 +33386,7 @@
       <c r="B71" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D71" s="54" t="s">
+      <c r="D71" s="35" t="s">
         <v>462</v>
       </c>
     </row>
@@ -32001,7 +33397,7 @@
       <c r="B72" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="54" t="s">
+      <c r="D72" s="35" t="s">
         <v>463</v>
       </c>
     </row>
@@ -32012,7 +33408,7 @@
       <c r="B73" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="54" t="s">
+      <c r="D73" s="35" t="s">
         <v>464</v>
       </c>
     </row>
@@ -32023,7 +33419,7 @@
       <c r="B74" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D74" s="54" t="s">
+      <c r="D74" s="35" t="s">
         <v>465</v>
       </c>
     </row>
@@ -32034,7 +33430,7 @@
       <c r="B75" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="54" t="s">
+      <c r="D75" s="35" t="s">
         <v>466</v>
       </c>
     </row>
@@ -32045,7 +33441,7 @@
       <c r="B76" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="54" t="s">
+      <c r="D76" s="35" t="s">
         <v>467</v>
       </c>
     </row>
@@ -32056,7 +33452,7 @@
       <c r="B77" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D77" s="54" t="s">
+      <c r="D77" s="35" t="s">
         <v>468</v>
       </c>
     </row>
@@ -32067,7 +33463,7 @@
       <c r="B78" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D78" s="54" t="s">
+      <c r="D78" s="35" t="s">
         <v>469</v>
       </c>
     </row>
@@ -32078,7 +33474,7 @@
       <c r="B79" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="54" t="s">
+      <c r="D79" s="35" t="s">
         <v>470</v>
       </c>
     </row>
@@ -32089,7 +33485,7 @@
       <c r="B80" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D80" s="54" t="s">
+      <c r="D80" s="35" t="s">
         <v>471</v>
       </c>
     </row>
@@ -32100,7 +33496,7 @@
       <c r="B81" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D81" s="54" t="s">
+      <c r="D81" s="35" t="s">
         <v>472</v>
       </c>
     </row>
@@ -32111,7 +33507,7 @@
       <c r="B82" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D82" s="55" t="s">
+      <c r="D82" s="36" t="s">
         <v>473</v>
       </c>
     </row>
@@ -32122,7 +33518,7 @@
       <c r="B83" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D83" s="54" t="s">
+      <c r="D83" s="35" t="s">
         <v>474</v>
       </c>
     </row>
@@ -32133,7 +33529,7 @@
       <c r="B84" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D84" s="54" t="s">
+      <c r="D84" s="35" t="s">
         <v>475</v>
       </c>
     </row>
@@ -32144,7 +33540,7 @@
       <c r="B85" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D85" s="54" t="s">
+      <c r="D85" s="35" t="s">
         <v>476</v>
       </c>
     </row>
@@ -32155,7 +33551,7 @@
       <c r="B86" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="D86" s="55" t="s">
+      <c r="D86" s="36" t="s">
         <v>477</v>
       </c>
     </row>
@@ -32166,7 +33562,7 @@
       <c r="B87" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="54" t="s">
+      <c r="D87" s="35" t="s">
         <v>478</v>
       </c>
     </row>
@@ -32177,7 +33573,7 @@
       <c r="B88" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D88" s="54" t="s">
+      <c r="D88" s="35" t="s">
         <v>479</v>
       </c>
     </row>
@@ -32188,7 +33584,7 @@
       <c r="B89" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D89" s="54" t="s">
+      <c r="D89" s="35" t="s">
         <v>480</v>
       </c>
     </row>
@@ -32199,7 +33595,7 @@
       <c r="B90" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D90" s="54" t="s">
+      <c r="D90" s="35" t="s">
         <v>481</v>
       </c>
     </row>
@@ -32210,7 +33606,7 @@
       <c r="B91" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D91" s="54" t="s">
+      <c r="D91" s="35" t="s">
         <v>482</v>
       </c>
     </row>
@@ -32221,7 +33617,7 @@
       <c r="B92" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D92" s="54" t="s">
+      <c r="D92" s="35" t="s">
         <v>483</v>
       </c>
     </row>
@@ -32232,7 +33628,7 @@
       <c r="B93" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="D93" s="54" t="s">
+      <c r="D93" s="35" t="s">
         <v>484</v>
       </c>
     </row>
@@ -32243,7 +33639,7 @@
       <c r="B94" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="D94" s="54" t="s">
+      <c r="D94" s="35" t="s">
         <v>485</v>
       </c>
     </row>
@@ -32254,7 +33650,7 @@
       <c r="B95" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D95" s="54" t="s">
+      <c r="D95" s="35" t="s">
         <v>486</v>
       </c>
     </row>
@@ -32265,7 +33661,7 @@
       <c r="B96" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="D96" s="55" t="s">
+      <c r="D96" s="36" t="s">
         <v>487</v>
       </c>
     </row>
@@ -32276,7 +33672,7 @@
       <c r="B97" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="D97" s="54" t="s">
+      <c r="D97" s="35" t="s">
         <v>488</v>
       </c>
     </row>
@@ -32287,7 +33683,7 @@
       <c r="B98" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="D98" s="54" t="s">
+      <c r="D98" s="35" t="s">
         <v>489</v>
       </c>
     </row>
@@ -32298,7 +33694,7 @@
       <c r="B99" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D99" s="54" t="s">
+      <c r="D99" s="35" t="s">
         <v>490</v>
       </c>
     </row>
@@ -32309,7 +33705,7 @@
       <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D100" s="54" t="s">
+      <c r="D100" s="35" t="s">
         <v>491</v>
       </c>
     </row>
@@ -32320,7 +33716,7 @@
       <c r="B101" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D101" s="54" t="s">
+      <c r="D101" s="35" t="s">
         <v>492</v>
       </c>
     </row>
@@ -32331,7 +33727,7 @@
       <c r="B102" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="54" t="s">
+      <c r="D102" s="35" t="s">
         <v>493</v>
       </c>
     </row>
@@ -32342,7 +33738,7 @@
       <c r="B103" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D103" s="54" t="s">
+      <c r="D103" s="35" t="s">
         <v>494</v>
       </c>
     </row>
@@ -32353,7 +33749,7 @@
       <c r="B104" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D104" s="54" t="s">
+      <c r="D104" s="35" t="s">
         <v>495</v>
       </c>
     </row>
@@ -32364,7 +33760,7 @@
       <c r="B105" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D105" s="55" t="s">
+      <c r="D105" s="36" t="s">
         <v>496</v>
       </c>
     </row>
@@ -32375,7 +33771,7 @@
       <c r="B106" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D106" s="55" t="s">
+      <c r="D106" s="36" t="s">
         <v>497</v>
       </c>
     </row>
@@ -32386,7 +33782,7 @@
       <c r="B107" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D107" s="54" t="s">
+      <c r="D107" s="35" t="s">
         <v>498</v>
       </c>
     </row>
@@ -32408,7 +33804,7 @@
       <c r="B109" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D109" s="56" t="s">
+      <c r="D109" s="37" t="s">
         <v>500</v>
       </c>
     </row>
@@ -32441,7 +33837,7 @@
       <c r="B112" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D112" s="54" t="s">
+      <c r="D112" s="35" t="s">
         <v>503</v>
       </c>
     </row>
@@ -32916,7 +34312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13254DC6-374D-4986-96B0-F1A090138EDE}">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -32937,12 +34333,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>

--- a/wwwroot/template/HistoryQuote.xlsx
+++ b/wwwroot/template/HistoryQuote.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8769F39-793F-4CFA-932C-4AFC1943D9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
@@ -2880,7 +2880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2951,15 +2951,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2969,11 +2960,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2982,69 +2969,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3072,30 +2996,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3145,9 +3045,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3156,6 +3053,96 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3624,19 +3611,19 @@
       <c r="AF2" s="9"/>
     </row>
     <row r="3" spans="1:36" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="70" t="s">
         <v>382</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
       <c r="L3" s="18"/>
       <c r="M3" s="18"/>
       <c r="N3" s="18"/>
@@ -3663,223 +3650,223 @@
       <c r="A4" s="22">
         <v>1</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="22">
         <v>2</v>
       </c>
       <c r="E4" s="22">
         <v>3</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="22">
         <v>4</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="22">
         <v>5</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="22">
         <v>6</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="22">
         <v>7</v>
       </c>
-      <c r="J4" s="25">
-        <v>8</v>
-      </c>
-      <c r="K4" s="25">
+      <c r="J4" s="22">
+        <v>8</v>
+      </c>
+      <c r="K4" s="22">
         <v>9</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="22">
         <v>10</v>
       </c>
-      <c r="M4" s="25">
+      <c r="M4" s="22">
         <v>11</v>
       </c>
-      <c r="N4" s="25">
+      <c r="N4" s="22">
         <v>12</v>
       </c>
-      <c r="O4" s="45">
+      <c r="O4" s="61">
         <f>N4+1</f>
         <v>13</v>
       </c>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="47"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="63"/>
       <c r="U4" s="24">
         <v>14</v>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="22">
         <f>U4+1</f>
         <v>15</v>
       </c>
-      <c r="W4" s="25">
+      <c r="W4" s="22">
         <f t="shared" ref="W4:AG4" si="0">V4+1</f>
         <v>16</v>
       </c>
-      <c r="X4" s="25">
+      <c r="X4" s="22">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="Y4" s="25">
+      <c r="Y4" s="22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="Z4" s="25">
+      <c r="Z4" s="22">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="AA4" s="25">
+      <c r="AA4" s="22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="AB4" s="25">
+      <c r="AB4" s="22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AC4" s="25">
+      <c r="AC4" s="22">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AD4" s="25">
+      <c r="AD4" s="22">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="AE4" s="25">
+      <c r="AE4" s="22">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AF4" s="25">
+      <c r="AF4" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AG4" s="25">
+      <c r="AG4" s="22">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25">
+      <c r="AH4" s="22"/>
+      <c r="AI4" s="22"/>
+      <c r="AJ4" s="22">
         <f>AG4+1</f>
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:36" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="64" t="s">
         <v>390</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="64" t="s">
         <v>391</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="64" t="s">
         <v>333</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="64" t="s">
         <v>334</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="64" t="s">
         <v>335</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="64" t="s">
         <v>338</v>
       </c>
-      <c r="J5" s="39" t="s">
+      <c r="J5" s="64" t="s">
         <v>340</v>
       </c>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="64" t="s">
         <v>341</v>
       </c>
-      <c r="L5" s="39" t="s">
+      <c r="L5" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="M5" s="39" t="s">
+      <c r="M5" s="64" t="s">
         <v>342</v>
       </c>
-      <c r="N5" s="39" t="s">
+      <c r="N5" s="64" t="s">
         <v>343</v>
       </c>
-      <c r="O5" s="48" t="s">
+      <c r="O5" s="66" t="s">
         <v>349</v>
       </c>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="39" t="s">
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="V5" s="39" t="s">
+      <c r="V5" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="W5" s="39" t="s">
+      <c r="W5" s="64" t="s">
         <v>350</v>
       </c>
-      <c r="X5" s="39" t="s">
+      <c r="X5" s="64" t="s">
         <v>351</v>
       </c>
-      <c r="Y5" s="39" t="s">
+      <c r="Y5" s="64" t="s">
         <v>355</v>
       </c>
-      <c r="Z5" s="39" t="s">
+      <c r="Z5" s="64" t="s">
         <v>356</v>
       </c>
-      <c r="AA5" s="39" t="s">
+      <c r="AA5" s="64" t="s">
         <v>357</v>
       </c>
-      <c r="AB5" s="39" t="s">
+      <c r="AB5" s="64" t="s">
         <v>358</v>
       </c>
-      <c r="AC5" s="39" t="s">
+      <c r="AC5" s="64" t="s">
         <v>359</v>
       </c>
-      <c r="AD5" s="39" t="s">
+      <c r="AD5" s="64" t="s">
         <v>360</v>
       </c>
-      <c r="AE5" s="39" t="s">
+      <c r="AE5" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="AF5" s="39" t="s">
+      <c r="AF5" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="AG5" s="38" t="s">
+      <c r="AG5" s="69" t="s">
         <v>363</v>
       </c>
-      <c r="AH5" s="38" t="s">
+      <c r="AH5" s="69" t="s">
         <v>364</v>
       </c>
-      <c r="AI5" s="39" t="s">
+      <c r="AI5" s="64" t="s">
         <v>388</v>
       </c>
-      <c r="AJ5" s="38" t="s">
+      <c r="AJ5" s="69" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:36" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
+      <c r="A6" s="73"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
       <c r="O6" s="19" t="s">
         <v>344</v>
       </c>
@@ -3898,22 +3885,22 @@
       <c r="T6" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="U6" s="40"/>
-      <c r="V6" s="40"/>
-      <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="40"/>
-      <c r="AA6" s="40"/>
-      <c r="AB6" s="40"/>
-      <c r="AC6" s="40"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="40"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="40"/>
-      <c r="AJ6" s="38"/>
+      <c r="U6" s="65"/>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="65"/>
+      <c r="AF6" s="65"/>
+      <c r="AG6" s="69"/>
+      <c r="AH6" s="69"/>
+      <c r="AI6" s="65"/>
+      <c r="AJ6" s="69"/>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
@@ -30797,11 +30784,18 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="Z5:Z6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
@@ -30817,19 +30811,12 @@
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
     <mergeCell ref="U5:U6"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="Z5:Z6"/>
     <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:T5"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC7:AC566" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -30879,24 +30866,24 @@
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="6" width="23.85546875" style="32" customWidth="1"/>
+    <col min="5" max="6" width="23.85546875" customWidth="1"/>
     <col min="7" max="7" width="92.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="19" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
       <c r="E2" s="20" t="s">
         <v>329</v>
       </c>
@@ -30906,11 +30893,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="79" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
       <c r="E3" s="20" t="s">
         <v>329</v>
       </c>
@@ -30922,13 +30909,13 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="28">
+      <c r="B4" s="25">
         <v>1</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="57"/>
+      <c r="D4" s="76"/>
       <c r="E4" s="20" t="s">
         <v>324</v>
       </c>
@@ -30938,13 +30925,13 @@
       <c r="G4" s="21"/>
     </row>
     <row r="5" spans="2:7" ht="30.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="28">
+      <c r="B5" s="25">
         <v>2</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="77" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="52"/>
+      <c r="D5" s="78"/>
       <c r="E5" s="20" t="s">
         <v>324</v>
       </c>
@@ -30953,13 +30940,13 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="28">
+      <c r="B6" s="25">
         <v>3</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="77" t="s">
         <v>334</v>
       </c>
-      <c r="D6" s="52"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="20" t="s">
         <v>329</v>
       </c>
@@ -30971,13 +30958,13 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="28">
+      <c r="B7" s="25">
         <v>4</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="77" t="s">
         <v>335</v>
       </c>
-      <c r="D7" s="52"/>
+      <c r="D7" s="78"/>
       <c r="E7" s="20" t="s">
         <v>329</v>
       </c>
@@ -30989,13 +30976,13 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="96" x14ac:dyDescent="0.25">
-      <c r="B8" s="28">
+      <c r="B8" s="25">
         <v>5</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="77" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="78"/>
       <c r="E8" s="20" t="s">
         <v>326</v>
       </c>
@@ -31007,13 +30994,13 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="28">
+      <c r="B9" s="25">
         <v>6</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="77" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="78"/>
       <c r="E9" s="20" t="s">
         <v>324</v>
       </c>
@@ -31025,13 +31012,13 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B10" s="28">
+      <c r="B10" s="25">
         <v>7</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="77" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="78"/>
       <c r="E10" s="20" t="s">
         <v>329</v>
       </c>
@@ -31043,13 +31030,13 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="28">
-        <v>8</v>
-      </c>
-      <c r="C11" s="51" t="s">
+      <c r="B11" s="25">
+        <v>8</v>
+      </c>
+      <c r="C11" s="77" t="s">
         <v>340</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="78"/>
       <c r="E11" s="20" t="s">
         <v>329</v>
       </c>
@@ -31061,61 +31048,61 @@
       </c>
     </row>
     <row r="12" spans="2:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="28">
+      <c r="B12" s="25">
         <v>9</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="77" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="52"/>
+      <c r="D12" s="78"/>
       <c r="E12" s="20" t="s">
         <v>329</v>
       </c>
       <c r="F12" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="G12" s="31"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="28">
+      <c r="B13" s="25">
         <v>10</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="77" t="s">
         <v>339</v>
       </c>
-      <c r="D13" s="52"/>
+      <c r="D13" s="78"/>
       <c r="E13" s="20" t="s">
         <v>324</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="G13" s="31"/>
+      <c r="G13" s="28"/>
     </row>
     <row r="14" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="28">
+      <c r="B14" s="25">
         <v>11</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="77" t="s">
         <v>342</v>
       </c>
-      <c r="D14" s="52"/>
+      <c r="D14" s="78"/>
       <c r="E14" s="20" t="s">
         <v>324</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="G14" s="31"/>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" spans="2:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="28">
+      <c r="B15" s="25">
         <v>12</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="77" t="s">
         <v>343</v>
       </c>
-      <c r="D15" s="52"/>
+      <c r="D15" s="78"/>
       <c r="E15" s="20" t="s">
         <v>329</v>
       </c>
@@ -31127,14 +31114,14 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="54">
+      <c r="B16" s="80">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="74" t="s">
         <v>349</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="26" t="s">
         <v>344</v>
       </c>
       <c r="E16" s="20" t="s">
@@ -31148,9 +31135,9 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="29" t="s">
+      <c r="B17" s="80"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="26" t="s">
         <v>345</v>
       </c>
       <c r="E17" s="20" t="s">
@@ -31164,9 +31151,9 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="29" t="s">
+      <c r="B18" s="80"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="26" t="s">
         <v>346</v>
       </c>
       <c r="E18" s="20" t="s">
@@ -31180,9 +31167,9 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="29" t="s">
+      <c r="B19" s="80"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="26" t="s">
         <v>347</v>
       </c>
       <c r="E19" s="20" t="s">
@@ -31196,9 +31183,9 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="29" t="s">
+      <c r="B20" s="80"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="26" t="s">
         <v>348</v>
       </c>
       <c r="E20" s="20" t="s">
@@ -31212,9 +31199,9 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="54"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="29" t="s">
+      <c r="B21" s="80"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="26" t="s">
         <v>352</v>
       </c>
       <c r="E21" s="20" t="s">
@@ -31228,13 +31215,13 @@
       </c>
     </row>
     <row r="22" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="30">
+      <c r="B22" s="27">
         <v>14</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="77" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="52"/>
+      <c r="D22" s="78"/>
       <c r="E22" s="20" t="s">
         <v>326</v>
       </c>
@@ -31246,14 +31233,14 @@
       </c>
     </row>
     <row r="23" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="28">
+      <c r="B23" s="25">
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="77" t="s">
         <v>354</v>
       </c>
-      <c r="D23" s="52"/>
+      <c r="D23" s="78"/>
       <c r="E23" s="20" t="s">
         <v>326</v>
       </c>
@@ -31265,14 +31252,14 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="28">
+      <c r="B24" s="25">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="77" t="s">
         <v>350</v>
       </c>
-      <c r="D24" s="52"/>
+      <c r="D24" s="78"/>
       <c r="E24" s="20" t="s">
         <v>326</v>
       </c>
@@ -31284,14 +31271,14 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="28">
+      <c r="B25" s="25">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="77" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="52"/>
+      <c r="D25" s="78"/>
       <c r="E25" s="20" t="s">
         <v>326</v>
       </c>
@@ -31303,14 +31290,14 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="60.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="28">
+      <c r="B26" s="25">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="77" t="s">
         <v>355</v>
       </c>
-      <c r="D26" s="52"/>
+      <c r="D26" s="78"/>
       <c r="E26" s="20" t="s">
         <v>331</v>
       </c>
@@ -31322,14 +31309,14 @@
       </c>
     </row>
     <row r="27" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="28">
+      <c r="B27" s="25">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="77" t="s">
         <v>356</v>
       </c>
-      <c r="D27" s="52"/>
+      <c r="D27" s="78"/>
       <c r="E27" s="20" t="s">
         <v>329</v>
       </c>
@@ -31341,14 +31328,14 @@
       </c>
     </row>
     <row r="28" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="28">
+      <c r="B28" s="25">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="77" t="s">
         <v>357</v>
       </c>
-      <c r="D28" s="52"/>
+      <c r="D28" s="78"/>
       <c r="E28" s="20" t="s">
         <v>329</v>
       </c>
@@ -31360,14 +31347,14 @@
       </c>
     </row>
     <row r="29" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="28">
+      <c r="B29" s="25">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="77" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="52"/>
+      <c r="D29" s="78"/>
       <c r="E29" s="20" t="s">
         <v>329</v>
       </c>
@@ -31379,14 +31366,14 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="28">
+      <c r="B30" s="25">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="77" t="s">
         <v>359</v>
       </c>
-      <c r="D30" s="52"/>
+      <c r="D30" s="78"/>
       <c r="E30" s="20" t="s">
         <v>324</v>
       </c>
@@ -31398,14 +31385,14 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="28">
+      <c r="B31" s="25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="77" t="s">
         <v>360</v>
       </c>
-      <c r="D31" s="52"/>
+      <c r="D31" s="78"/>
       <c r="E31" s="20" t="s">
         <v>324</v>
       </c>
@@ -31417,14 +31404,14 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="28">
+      <c r="B32" s="25">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="77" t="s">
         <v>361</v>
       </c>
-      <c r="D32" s="52"/>
+      <c r="D32" s="78"/>
       <c r="E32" s="20" t="s">
         <v>324</v>
       </c>
@@ -31434,14 +31421,14 @@
       <c r="G32" s="20"/>
     </row>
     <row r="33" spans="2:7" ht="78.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="28">
+      <c r="B33" s="25">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="77" t="s">
         <v>362</v>
       </c>
-      <c r="D33" s="52"/>
+      <c r="D33" s="78"/>
       <c r="E33" s="20" t="s">
         <v>324</v>
       </c>
@@ -31453,14 +31440,14 @@
       </c>
     </row>
     <row r="34" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="28">
+      <c r="B34" s="25">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="74" t="s">
         <v>363</v>
       </c>
-      <c r="D34" s="55"/>
+      <c r="D34" s="74"/>
       <c r="E34" s="20" t="s">
         <v>326</v>
       </c>
@@ -31472,27 +31459,41 @@
       </c>
     </row>
     <row r="35" spans="2:7" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="28">
+      <c r="B35" s="25">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="74" t="s">
         <v>364</v>
       </c>
-      <c r="D35" s="55"/>
+      <c r="D35" s="74"/>
       <c r="E35" s="20" t="s">
         <v>326</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="21" t="s">
         <v>381</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -31509,20 +31510,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -31538,1007 +31525,1009 @@
     <col min="8" max="8" width="52.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="59"/>
-      <c r="B1" s="60" t="s">
+    <row r="1" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="33"/>
+      <c r="B1" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="37" t="s">
         <v>506</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="38" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="59"/>
-      <c r="E2" s="59"/>
-    </row>
-    <row r="3" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+    <row r="2" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="E2" s="33"/>
+    </row>
+    <row r="3" spans="1:33" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="39" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
+    <row r="4" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="40">
         <v>1</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="22">
         <v>2</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="22">
         <v>3</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="22">
         <v>4</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="22">
         <v>5</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="22">
         <v>6</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="22">
         <v>7</v>
       </c>
-      <c r="H4" s="25">
-        <v>8</v>
-      </c>
-      <c r="I4" s="25">
+      <c r="H4" s="22">
+        <v>8</v>
+      </c>
+      <c r="I4" s="22">
         <v>9</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="22">
         <v>10</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="22">
         <v>11</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="22">
         <v>12</v>
       </c>
-      <c r="M4" s="45">
+      <c r="M4" s="61">
         <f>L4+1</f>
         <v>13</v>
       </c>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="34">
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="24">
         <v>14</v>
       </c>
-      <c r="T4" s="25">
+      <c r="T4" s="22">
         <f>S4+1</f>
         <v>15</v>
       </c>
-      <c r="U4" s="25">
+      <c r="U4" s="22">
         <f t="shared" ref="U4:AF4" si="0">T4+1</f>
         <v>16</v>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="22">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="W4" s="25">
+      <c r="W4" s="22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="X4" s="25">
+      <c r="X4" s="22">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="Y4" s="25">
+      <c r="Y4" s="22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Z4" s="25">
+      <c r="Z4" s="22">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="AA4" s="25">
+      <c r="AA4" s="22">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AB4" s="25">
+      <c r="AB4" s="22">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="AC4" s="25">
+      <c r="AC4" s="22">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AD4" s="25">
+      <c r="AD4" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="AE4" s="25">
+      <c r="AE4" s="22">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="AF4" s="33">
+      <c r="AF4" s="29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AG4" s="25">
+      <c r="AG4" s="22">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+    <row r="5" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="83" t="s">
         <v>333</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="83" t="s">
         <v>334</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="83" t="s">
         <v>335</v>
       </c>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="83" t="s">
         <v>336</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" s="83" t="s">
         <v>337</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="83" t="s">
         <v>338</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="83" t="s">
         <v>340</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="83" t="s">
         <v>341</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="83" t="s">
         <v>339</v>
       </c>
-      <c r="K5" s="69" t="s">
+      <c r="K5" s="83" t="s">
         <v>342</v>
       </c>
-      <c r="L5" s="69" t="s">
+      <c r="L5" s="83" t="s">
         <v>343</v>
       </c>
-      <c r="M5" s="70" t="s">
+      <c r="M5" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="72"/>
-      <c r="S5" s="69" t="s">
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="86"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="83" t="s">
         <v>353</v>
       </c>
-      <c r="T5" s="69" t="s">
+      <c r="T5" s="83" t="s">
         <v>354</v>
       </c>
-      <c r="U5" s="69" t="s">
+      <c r="U5" s="83" t="s">
         <v>350</v>
       </c>
-      <c r="V5" s="69" t="s">
+      <c r="V5" s="83" t="s">
         <v>351</v>
       </c>
-      <c r="W5" s="69" t="s">
+      <c r="W5" s="83" t="s">
         <v>355</v>
       </c>
-      <c r="X5" s="69" t="s">
+      <c r="X5" s="83" t="s">
         <v>356</v>
       </c>
-      <c r="Y5" s="69" t="s">
+      <c r="Y5" s="83" t="s">
         <v>357</v>
       </c>
-      <c r="Z5" s="69" t="s">
+      <c r="Z5" s="83" t="s">
         <v>358</v>
       </c>
-      <c r="AA5" s="69" t="s">
+      <c r="AA5" s="83" t="s">
         <v>359</v>
       </c>
-      <c r="AB5" s="69" t="s">
+      <c r="AB5" s="83" t="s">
         <v>360</v>
       </c>
-      <c r="AC5" s="69" t="s">
+      <c r="AC5" s="83" t="s">
         <v>361</v>
       </c>
-      <c r="AD5" s="69" t="s">
+      <c r="AD5" s="83" t="s">
         <v>362</v>
       </c>
-      <c r="AE5" s="73" t="s">
+      <c r="AE5" s="82" t="s">
         <v>363</v>
       </c>
-      <c r="AF5" s="70" t="s">
+      <c r="AF5" s="85" t="s">
         <v>364</v>
       </c>
-      <c r="AG5" s="73" t="s">
+      <c r="AG5" s="82" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="74"/>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="76" t="s">
+    <row r="6" spans="1:33" s="41" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="89"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="N6" s="76" t="s">
+      <c r="N6" s="42" t="s">
         <v>345</v>
       </c>
-      <c r="O6" s="76" t="s">
+      <c r="O6" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="P6" s="76" t="s">
+      <c r="P6" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="Q6" s="76" t="s">
+      <c r="Q6" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="R6" s="76" t="s">
+      <c r="R6" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="S6" s="75"/>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="75"/>
-      <c r="W6" s="75"/>
-      <c r="X6" s="75"/>
-      <c r="Y6" s="75"/>
-      <c r="Z6" s="75"/>
-      <c r="AA6" s="75"/>
-      <c r="AB6" s="75"/>
-      <c r="AC6" s="75"/>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="73"/>
-      <c r="AF6" s="70"/>
-      <c r="AG6" s="73"/>
-    </row>
-    <row r="7" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="77">
+      <c r="S6" s="84"/>
+      <c r="T6" s="84"/>
+      <c r="U6" s="84"/>
+      <c r="V6" s="84"/>
+      <c r="W6" s="84"/>
+      <c r="X6" s="84"/>
+      <c r="Y6" s="84"/>
+      <c r="Z6" s="84"/>
+      <c r="AA6" s="84"/>
+      <c r="AB6" s="84"/>
+      <c r="AC6" s="84"/>
+      <c r="AD6" s="84"/>
+      <c r="AE6" s="82"/>
+      <c r="AF6" s="85"/>
+      <c r="AG6" s="82"/>
+    </row>
+    <row r="7" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
         <v>1</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="44">
         <v>3110</v>
       </c>
-      <c r="C7" s="79" t="e">
+      <c r="C7" s="45" t="e">
         <f>VLOOKUP(B7,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80"/>
-      <c r="F7" s="78" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="44" t="s">
         <v>510</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81" t="str">
+      <c r="G7" s="47"/>
+      <c r="H7" s="47" t="str">
         <f>L7&amp;"có hình dáng dạng "&amp;M7&amp;" chất liệu "&amp;N7&amp;" thành phần hóa chất: "&amp;O7&amp;" có kích thước "&amp;P7&amp;" dùng để "&amp;R7&amp;" cho "&amp;Q7</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I7" s="81"/>
-      <c r="J7" s="78">
+      <c r="I7" s="47"/>
+      <c r="J7" s="44">
         <v>10</v>
       </c>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="84" t="s">
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="47"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="X7" s="81"/>
-      <c r="Y7" s="81"/>
-      <c r="Z7" s="81"/>
-      <c r="AA7" s="85" t="s">
+      <c r="X7" s="47"/>
+      <c r="Y7" s="47"/>
+      <c r="Z7" s="47"/>
+      <c r="AA7" s="51" t="s">
         <v>512</v>
       </c>
-      <c r="AB7" s="80"/>
-      <c r="AC7" s="86">
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="52">
         <v>46143</v>
       </c>
-      <c r="AD7" s="86">
+      <c r="AD7" s="52">
         <v>46132</v>
       </c>
-      <c r="AE7" s="80"/>
-      <c r="AF7" s="87"/>
-      <c r="AG7" s="80"/>
-    </row>
-    <row r="8" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="77">
+      <c r="AE7" s="46"/>
+      <c r="AF7" s="53"/>
+      <c r="AG7" s="46"/>
+    </row>
+    <row r="8" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
         <v>2</v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="44">
         <v>3110</v>
       </c>
-      <c r="C8" s="79" t="e">
+      <c r="C8" s="45" t="e">
         <f>VLOOKUP(B8,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D8" s="79"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="78" t="s">
+      <c r="D8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="44" t="s">
         <v>513</v>
       </c>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81" t="str">
+      <c r="G8" s="47"/>
+      <c r="H8" s="47" t="str">
         <f t="shared" ref="H8:H9" si="1">L8&amp;"có hình dáng dạng "&amp;M8&amp;" chất liệu "&amp;N8&amp;" thành phần hóa chất: "&amp;O8&amp;" có kích thước "&amp;P8&amp;" dùng để "&amp;R8&amp;" cho "&amp;Q8</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="78">
+      <c r="I8" s="47"/>
+      <c r="J8" s="44">
         <v>10</v>
       </c>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="82"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="80"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="80"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="84" t="s">
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="47"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="50" t="s">
         <v>514</v>
       </c>
-      <c r="X8" s="81"/>
-      <c r="Y8" s="81"/>
-      <c r="Z8" s="81"/>
-      <c r="AA8" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB8" s="80"/>
-      <c r="AC8" s="86">
+      <c r="X8" s="47"/>
+      <c r="Y8" s="47"/>
+      <c r="Z8" s="47"/>
+      <c r="AA8" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="46"/>
+      <c r="AC8" s="52">
         <v>46143</v>
       </c>
-      <c r="AD8" s="86">
+      <c r="AD8" s="52">
         <v>46132</v>
       </c>
-      <c r="AE8" s="80"/>
-      <c r="AF8" s="87"/>
-      <c r="AG8" s="80"/>
-    </row>
-    <row r="9" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="77">
+      <c r="AE8" s="46"/>
+      <c r="AF8" s="53"/>
+      <c r="AG8" s="46"/>
+    </row>
+    <row r="9" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
         <v>3</v>
       </c>
-      <c r="B9" s="78">
+      <c r="B9" s="44">
         <v>3110</v>
       </c>
-      <c r="C9" s="79" t="e">
+      <c r="C9" s="45" t="e">
         <f>VLOOKUP(B9,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="78" t="s">
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81" t="str">
+      <c r="G9" s="47"/>
+      <c r="H9" s="47" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I9" s="81"/>
-      <c r="J9" s="78">
+      <c r="I9" s="47"/>
+      <c r="J9" s="44">
         <v>10</v>
       </c>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="81"/>
-      <c r="Q9" s="81"/>
-      <c r="R9" s="81"/>
-      <c r="S9" s="80"/>
-      <c r="T9" s="80"/>
-      <c r="U9" s="80"/>
-      <c r="V9" s="80"/>
-      <c r="W9" s="84" t="s">
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="50" t="s">
         <v>516</v>
       </c>
-      <c r="X9" s="81"/>
-      <c r="Y9" s="81"/>
-      <c r="Z9" s="81"/>
-      <c r="AA9" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="80"/>
-      <c r="AC9" s="86">
+      <c r="X9" s="47"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
+      <c r="AA9" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="52">
         <v>46143</v>
       </c>
-      <c r="AD9" s="86">
+      <c r="AD9" s="52">
         <v>46132</v>
       </c>
-      <c r="AE9" s="80"/>
-      <c r="AF9" s="87"/>
-      <c r="AG9" s="80"/>
-    </row>
-    <row r="10" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="H10" s="62" t="str">
+      <c r="AE9" s="46"/>
+      <c r="AF9" s="53"/>
+      <c r="AG9" s="46"/>
+    </row>
+    <row r="10" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H10" s="36" t="str">
         <f t="shared" ref="H10:H11" si="2">M10&amp;" "&amp;N10&amp;" "&amp;O10&amp;""&amp;P10&amp;" "&amp;Q10&amp;" "&amp;R10</f>
         <v xml:space="preserve">    </v>
       </c>
-      <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="AA10" s="89"/>
-      <c r="AC10" s="90"/>
-      <c r="AD10" s="90"/>
-    </row>
-    <row r="11" spans="1:33" s="62" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="H11" s="62" t="str">
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="AA10" s="55"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="56"/>
+    </row>
+    <row r="11" spans="1:33" s="36" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="H11" s="36" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">    </v>
       </c>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="AA11" s="89"/>
-      <c r="AC11" s="90"/>
-      <c r="AD11" s="90"/>
-    </row>
-    <row r="12" spans="1:33" s="62" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="65" t="s">
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="AA11" s="55"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="56"/>
+    </row>
+    <row r="12" spans="1:33" s="36" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="66">
+    <row r="13" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="40">
         <v>1</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="22">
         <v>2</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="22">
         <v>3</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="22">
         <v>4</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="22">
         <v>5</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="22">
         <v>6</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="22">
         <v>7</v>
       </c>
-      <c r="H13" s="25">
-        <v>8</v>
-      </c>
-      <c r="I13" s="25">
+      <c r="H13" s="22">
+        <v>8</v>
+      </c>
+      <c r="I13" s="22">
         <v>9</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="22">
         <v>10</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="22">
         <v>11</v>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="22">
         <v>12</v>
       </c>
-      <c r="M13" s="45">
+      <c r="M13" s="61">
         <f>L13+1</f>
         <v>13</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="34">
+      <c r="N13" s="62"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="63"/>
+      <c r="S13" s="24">
         <v>14</v>
       </c>
-      <c r="T13" s="25">
+      <c r="T13" s="22">
         <f>S13+1</f>
         <v>15</v>
       </c>
-      <c r="U13" s="25">
+      <c r="U13" s="22">
         <f t="shared" ref="U13:AF13" si="3">T13+1</f>
         <v>16</v>
       </c>
-      <c r="V13" s="25">
+      <c r="V13" s="22">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="W13" s="25">
+      <c r="W13" s="22">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="X13" s="25">
+      <c r="X13" s="22">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="Y13" s="25">
+      <c r="Y13" s="22">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="Z13" s="25">
+      <c r="Z13" s="22">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="AA13" s="25">
+      <c r="AA13" s="22">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="AB13" s="25">
+      <c r="AB13" s="22">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="AC13" s="25">
+      <c r="AC13" s="22">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="AD13" s="25">
+      <c r="AD13" s="22">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="AE13" s="25">
+      <c r="AE13" s="22">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="AF13" s="91">
+      <c r="AF13" s="57">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="AG13" s="25">
+      <c r="AG13" s="22">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="68" t="s">
+    <row r="14" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="83" t="s">
         <v>333</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="83" t="s">
         <v>334</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="83" t="s">
         <v>335</v>
       </c>
-      <c r="E14" s="69" t="s">
+      <c r="E14" s="83" t="s">
         <v>336</v>
       </c>
-      <c r="F14" s="69" t="s">
+      <c r="F14" s="83" t="s">
         <v>337</v>
       </c>
-      <c r="G14" s="69" t="s">
+      <c r="G14" s="83" t="s">
         <v>338</v>
       </c>
-      <c r="H14" s="69" t="s">
+      <c r="H14" s="83" t="s">
         <v>340</v>
       </c>
-      <c r="I14" s="69" t="s">
+      <c r="I14" s="83" t="s">
         <v>341</v>
       </c>
-      <c r="J14" s="69" t="s">
+      <c r="J14" s="83" t="s">
         <v>339</v>
       </c>
-      <c r="K14" s="69" t="s">
+      <c r="K14" s="83" t="s">
         <v>342</v>
       </c>
-      <c r="L14" s="69" t="s">
+      <c r="L14" s="83" t="s">
         <v>343</v>
       </c>
-      <c r="M14" s="70" t="s">
+      <c r="M14" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="N14" s="71"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="69" t="s">
+      <c r="N14" s="86"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="86"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="83" t="s">
         <v>353</v>
       </c>
-      <c r="T14" s="69" t="s">
+      <c r="T14" s="83" t="s">
         <v>354</v>
       </c>
-      <c r="U14" s="69" t="s">
+      <c r="U14" s="83" t="s">
         <v>350</v>
       </c>
-      <c r="V14" s="69" t="s">
+      <c r="V14" s="83" t="s">
         <v>351</v>
       </c>
-      <c r="W14" s="69" t="s">
+      <c r="W14" s="83" t="s">
         <v>355</v>
       </c>
-      <c r="X14" s="69" t="s">
+      <c r="X14" s="83" t="s">
         <v>356</v>
       </c>
-      <c r="Y14" s="69" t="s">
+      <c r="Y14" s="83" t="s">
         <v>357</v>
       </c>
-      <c r="Z14" s="69" t="s">
+      <c r="Z14" s="83" t="s">
         <v>358</v>
       </c>
-      <c r="AA14" s="69" t="s">
+      <c r="AA14" s="83" t="s">
         <v>359</v>
       </c>
-      <c r="AB14" s="69" t="s">
+      <c r="AB14" s="83" t="s">
         <v>360</v>
       </c>
-      <c r="AC14" s="69" t="s">
+      <c r="AC14" s="83" t="s">
         <v>361</v>
       </c>
-      <c r="AD14" s="69" t="s">
+      <c r="AD14" s="83" t="s">
         <v>362</v>
       </c>
-      <c r="AE14" s="73" t="s">
+      <c r="AE14" s="82" t="s">
         <v>363</v>
       </c>
-      <c r="AF14" s="92" t="s">
+      <c r="AF14" s="81" t="s">
         <v>364</v>
       </c>
-      <c r="AG14" s="73" t="s">
+      <c r="AG14" s="82" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="15" spans="1:33" s="67" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="74"/>
-      <c r="B15" s="75"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="76" t="s">
+    <row r="15" spans="1:33" s="41" customFormat="1" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="89"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="N15" s="76" t="s">
+      <c r="N15" s="42" t="s">
         <v>345</v>
       </c>
-      <c r="O15" s="76" t="s">
+      <c r="O15" s="42" t="s">
         <v>346</v>
       </c>
-      <c r="P15" s="76" t="s">
+      <c r="P15" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="Q15" s="76" t="s">
+      <c r="Q15" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="R15" s="76" t="s">
+      <c r="R15" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="S15" s="75"/>
-      <c r="T15" s="75"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="75"/>
-      <c r="X15" s="75"/>
-      <c r="Y15" s="75"/>
-      <c r="Z15" s="75"/>
-      <c r="AA15" s="75"/>
-      <c r="AB15" s="75"/>
-      <c r="AC15" s="75"/>
-      <c r="AD15" s="75"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="92"/>
-      <c r="AG15" s="73"/>
-    </row>
-    <row r="16" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A16" s="77">
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="84"/>
+      <c r="AE15" s="82"/>
+      <c r="AF15" s="81"/>
+      <c r="AG15" s="82"/>
+    </row>
+    <row r="16" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="43">
         <v>1</v>
       </c>
-      <c r="B16" s="78">
+      <c r="B16" s="44">
         <v>3110</v>
       </c>
-      <c r="C16" s="79" t="e">
+      <c r="C16" s="45" t="e">
         <f>VLOOKUP(B16,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D16" s="78"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="81" t="str">
+      <c r="D16" s="44"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="47" t="str">
         <f>L16&amp;"có hình dáng dạng "&amp;M16&amp;" chất liệu "&amp;N16&amp;" thành phần hóa chất: "&amp;O16&amp;" có kích thước "&amp;P16&amp;" dùng để "&amp;R16&amp;" cho "&amp;Q16</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78">
+      <c r="I16" s="44"/>
+      <c r="J16" s="44">
         <v>10</v>
       </c>
-      <c r="K16" s="78" t="s">
+      <c r="K16" s="44" t="s">
         <v>518</v>
       </c>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="83"/>
-      <c r="T16" s="83"/>
-      <c r="U16" s="83"/>
-      <c r="V16" s="83"/>
-      <c r="W16" s="84" t="s">
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="X16" s="80"/>
-      <c r="Y16" s="81"/>
-      <c r="Z16" s="81"/>
-      <c r="AA16" s="85" t="s">
+      <c r="X16" s="46"/>
+      <c r="Y16" s="47"/>
+      <c r="Z16" s="47"/>
+      <c r="AA16" s="51" t="s">
         <v>512</v>
       </c>
-      <c r="AB16" s="80"/>
-      <c r="AC16" s="86">
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="52">
         <v>46143</v>
       </c>
-      <c r="AD16" s="86">
+      <c r="AD16" s="52">
         <v>46132</v>
       </c>
-      <c r="AE16" s="80"/>
-      <c r="AF16" s="94"/>
-      <c r="AG16" s="80"/>
-    </row>
-    <row r="17" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="77">
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="59"/>
+      <c r="AG16" s="46"/>
+    </row>
+    <row r="17" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="43">
         <v>2</v>
       </c>
-      <c r="B17" s="78">
+      <c r="B17" s="44">
         <v>3110</v>
       </c>
-      <c r="C17" s="79" t="e">
+      <c r="C17" s="45" t="e">
         <f>VLOOKUP(B17,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D17" s="78"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="81" t="str">
+      <c r="D17" s="44"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="47" t="str">
         <f t="shared" ref="H17:H19" si="4">L17&amp;"có hình dáng dạng "&amp;M17&amp;" chất liệu "&amp;N17&amp;" thành phần hóa chất: "&amp;O17&amp;" có kích thước "&amp;P17&amp;" dùng để "&amp;R17&amp;" cho "&amp;Q17</f>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78">
+      <c r="I17" s="44"/>
+      <c r="J17" s="44">
         <v>10</v>
       </c>
-      <c r="K17" s="78" t="s">
+      <c r="K17" s="44" t="s">
         <v>518</v>
       </c>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="93"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="78"/>
-      <c r="S17" s="80"/>
-      <c r="T17" s="80"/>
-      <c r="U17" s="80"/>
-      <c r="V17" s="80"/>
-      <c r="W17" s="84" t="s">
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="44"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="50" t="s">
         <v>514</v>
       </c>
-      <c r="X17" s="80"/>
-      <c r="Y17" s="81"/>
-      <c r="Z17" s="81"/>
-      <c r="AA17" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB17" s="80"/>
-      <c r="AC17" s="86">
+      <c r="X17" s="46"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="47"/>
+      <c r="AA17" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="52">
         <v>46143</v>
       </c>
-      <c r="AD17" s="86">
+      <c r="AD17" s="52">
         <v>46132</v>
       </c>
-      <c r="AE17" s="80"/>
-      <c r="AF17" s="94"/>
-      <c r="AG17" s="80"/>
-    </row>
-    <row r="18" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="77">
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="59"/>
+      <c r="AG17" s="46"/>
+    </row>
+    <row r="18" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="43">
         <v>3</v>
       </c>
-      <c r="B18" s="78">
+      <c r="B18" s="44">
         <v>3110</v>
       </c>
-      <c r="C18" s="79" t="e">
+      <c r="C18" s="45" t="e">
         <f>VLOOKUP(B18,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="81" t="str">
+      <c r="D18" s="44"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="47" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78">
+      <c r="I18" s="44"/>
+      <c r="J18" s="44">
         <v>10</v>
       </c>
-      <c r="K18" s="78" t="s">
+      <c r="K18" s="44" t="s">
         <v>518</v>
       </c>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="84" t="s">
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="44"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="44"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="50" t="s">
         <v>516</v>
       </c>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="81"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB18" s="80"/>
-      <c r="AC18" s="86">
+      <c r="X18" s="46"/>
+      <c r="Y18" s="47"/>
+      <c r="Z18" s="47"/>
+      <c r="AA18" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="46"/>
+      <c r="AC18" s="52">
         <v>46143</v>
       </c>
-      <c r="AD18" s="86">
+      <c r="AD18" s="52">
         <v>46132</v>
       </c>
-      <c r="AE18" s="80"/>
-      <c r="AF18" s="94"/>
-      <c r="AG18" s="80"/>
-    </row>
-    <row r="19" spans="1:33" s="67" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="77">
+      <c r="AE18" s="46"/>
+      <c r="AF18" s="59"/>
+      <c r="AG18" s="46"/>
+    </row>
+    <row r="19" spans="1:33" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="43">
         <v>3</v>
       </c>
-      <c r="B19" s="78">
+      <c r="B19" s="44">
         <v>3110</v>
       </c>
-      <c r="C19" s="79" t="e">
+      <c r="C19" s="45" t="e">
         <f>VLOOKUP(B19,[1]Master!D:E,2,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="81" t="str">
+      <c r="D19" s="44"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="47" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78">
+      <c r="I19" s="44"/>
+      <c r="J19" s="44">
         <v>10</v>
       </c>
-      <c r="K19" s="78" t="s">
+      <c r="K19" s="44" t="s">
         <v>518</v>
       </c>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="80"/>
-      <c r="U19" s="80"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="84" t="s">
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="50" t="s">
         <v>516</v>
       </c>
-      <c r="X19" s="80"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="81"/>
-      <c r="AA19" s="85" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB19" s="80"/>
-      <c r="AC19" s="86">
+      <c r="X19" s="46"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="47"/>
+      <c r="AA19" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB19" s="46"/>
+      <c r="AC19" s="52">
         <v>46143</v>
       </c>
-      <c r="AD19" s="86">
+      <c r="AD19" s="52">
         <v>46132</v>
       </c>
-      <c r="AE19" s="80"/>
-      <c r="AF19" s="94"/>
-      <c r="AG19" s="94"/>
-    </row>
-    <row r="20" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="95" t="s">
+      <c r="AE19" s="46"/>
+      <c r="AF19" s="59"/>
+      <c r="AG19" s="59"/>
+    </row>
+    <row r="20" spans="1:33" s="60" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="60" t="s">
         <v>519</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="60" t="s">
         <v>519</v>
       </c>
-      <c r="K20" s="95" t="s">
+      <c r="K20" s="60" t="s">
         <v>519</v>
       </c>
-      <c r="L20" s="95" t="s">
+      <c r="L20" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="M20" s="95" t="s">
+      <c r="M20" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="N20" s="95" t="s">
+      <c r="N20" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="O20" s="95" t="s">
+      <c r="O20" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="P20" s="95" t="s">
+      <c r="P20" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="Q20" s="95" t="s">
+      <c r="Q20" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="R20" s="95" t="s">
+      <c r="R20" s="60" t="s">
         <v>521</v>
       </c>
-      <c r="Y20" s="95" t="s">
+      <c r="Y20" s="60" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="21" spans="1:33" s="95" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
-      <c r="L21" s="95" t="s">
+    <row r="21" spans="1:33" s="60" customFormat="1" ht="10.5" x14ac:dyDescent="0.25">
+      <c r="L21" s="60" t="s">
         <v>523</v>
       </c>
-      <c r="Y21" s="95" t="s">
+      <c r="Y21" s="60" t="s">
         <v>524</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="AF14:AF15"/>
-    <mergeCell ref="AG14:AG15"/>
-    <mergeCell ref="Z14:Z15"/>
-    <mergeCell ref="AA14:AA15"/>
-    <mergeCell ref="AB14:AB15"/>
-    <mergeCell ref="AC14:AC15"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AE14:AE15"/>
-    <mergeCell ref="T14:T15"/>
-    <mergeCell ref="U14:U15"/>
-    <mergeCell ref="V14:V15"/>
-    <mergeCell ref="W14:W15"/>
-    <mergeCell ref="X14:X15"/>
-    <mergeCell ref="Y14:Y15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:R14"/>
-    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:R5"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="M13:R13"/>
     <mergeCell ref="A14:A15"/>
@@ -32555,28 +32544,26 @@
     <mergeCell ref="AD5:AD6"/>
     <mergeCell ref="AE5:AE6"/>
     <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:R5"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:R14"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="AF14:AF15"/>
+    <mergeCell ref="AG14:AG15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AC14:AC15"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AE14:AE15"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA7:AA11 AA16:AA18" xr:uid="{799C4DBD-0D65-4AB3-8350-D2591EB5B20C}">
@@ -32627,7 +32614,7 @@
       <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="30" t="s">
         <v>393</v>
       </c>
     </row>
@@ -32638,7 +32625,7 @@
       <c r="B3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="30" t="s">
         <v>394</v>
       </c>
     </row>
@@ -32649,7 +32636,7 @@
       <c r="B4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="30" t="s">
         <v>395</v>
       </c>
     </row>
@@ -32660,7 +32647,7 @@
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="30" t="s">
         <v>396</v>
       </c>
     </row>
@@ -32671,7 +32658,7 @@
       <c r="B6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="30" t="s">
         <v>397</v>
       </c>
     </row>
@@ -32682,7 +32669,7 @@
       <c r="B7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="30" t="s">
         <v>398</v>
       </c>
     </row>
@@ -32693,7 +32680,7 @@
       <c r="B8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="31" t="s">
         <v>399</v>
       </c>
     </row>
@@ -32704,7 +32691,7 @@
       <c r="B9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="31" t="s">
         <v>400</v>
       </c>
     </row>
@@ -32715,7 +32702,7 @@
       <c r="B10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="30" t="s">
         <v>401</v>
       </c>
     </row>
@@ -32726,7 +32713,7 @@
       <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="31" t="s">
         <v>402</v>
       </c>
     </row>
@@ -32737,7 +32724,7 @@
       <c r="B12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="30" t="s">
         <v>403</v>
       </c>
     </row>
@@ -32748,7 +32735,7 @@
       <c r="B13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="30" t="s">
         <v>404</v>
       </c>
     </row>
@@ -32759,7 +32746,7 @@
       <c r="B14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="D14" s="30" t="s">
         <v>405</v>
       </c>
     </row>
@@ -32770,7 +32757,7 @@
       <c r="B15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="30" t="s">
         <v>406</v>
       </c>
     </row>
@@ -32781,7 +32768,7 @@
       <c r="B16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="30" t="s">
         <v>407</v>
       </c>
     </row>
@@ -32792,7 +32779,7 @@
       <c r="B17" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="30" t="s">
         <v>408</v>
       </c>
     </row>
@@ -32803,7 +32790,7 @@
       <c r="B18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="30" t="s">
         <v>409</v>
       </c>
     </row>
@@ -32814,7 +32801,7 @@
       <c r="B19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="31" t="s">
         <v>410</v>
       </c>
     </row>
@@ -32825,7 +32812,7 @@
       <c r="B20" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="31" t="s">
         <v>411</v>
       </c>
     </row>
@@ -32836,7 +32823,7 @@
       <c r="B21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="31" t="s">
         <v>412</v>
       </c>
     </row>
@@ -32847,7 +32834,7 @@
       <c r="B22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="30" t="s">
         <v>413</v>
       </c>
     </row>
@@ -32858,7 +32845,7 @@
       <c r="B23" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="31" t="s">
         <v>414</v>
       </c>
     </row>
@@ -32869,7 +32856,7 @@
       <c r="B24" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="30" t="s">
         <v>415</v>
       </c>
     </row>
@@ -32880,7 +32867,7 @@
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="31" t="s">
         <v>416</v>
       </c>
     </row>
@@ -32891,7 +32878,7 @@
       <c r="B26" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="31" t="s">
         <v>417</v>
       </c>
     </row>
@@ -32902,7 +32889,7 @@
       <c r="B27" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="30" t="s">
         <v>418</v>
       </c>
     </row>
@@ -32913,7 +32900,7 @@
       <c r="B28" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="30" t="s">
         <v>419</v>
       </c>
     </row>
@@ -32924,7 +32911,7 @@
       <c r="B29" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="31" t="s">
         <v>420</v>
       </c>
     </row>
@@ -32935,7 +32922,7 @@
       <c r="B30" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="31" t="s">
         <v>421</v>
       </c>
     </row>
@@ -32946,7 +32933,7 @@
       <c r="B31" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="35" t="s">
+      <c r="D31" s="30" t="s">
         <v>422</v>
       </c>
     </row>
@@ -32957,7 +32944,7 @@
       <c r="B32" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="35" t="s">
+      <c r="D32" s="30" t="s">
         <v>423</v>
       </c>
     </row>
@@ -32968,7 +32955,7 @@
       <c r="B33" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="30" t="s">
         <v>424</v>
       </c>
     </row>
@@ -32979,7 +32966,7 @@
       <c r="B34" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="35" t="s">
+      <c r="D34" s="30" t="s">
         <v>425</v>
       </c>
     </row>
@@ -32990,7 +32977,7 @@
       <c r="B35" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="30" t="s">
         <v>426</v>
       </c>
     </row>
@@ -33001,7 +32988,7 @@
       <c r="B36" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="35" t="s">
+      <c r="D36" s="30" t="s">
         <v>427</v>
       </c>
     </row>
@@ -33012,7 +32999,7 @@
       <c r="B37" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="30" t="s">
         <v>428</v>
       </c>
     </row>
@@ -33023,7 +33010,7 @@
       <c r="B38" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="31" t="s">
         <v>429</v>
       </c>
     </row>
@@ -33034,7 +33021,7 @@
       <c r="B39" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="D39" s="30" t="s">
         <v>430</v>
       </c>
     </row>
@@ -33045,7 +33032,7 @@
       <c r="B40" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="30" t="s">
         <v>431</v>
       </c>
     </row>
@@ -33056,7 +33043,7 @@
       <c r="B41" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="30" t="s">
         <v>432</v>
       </c>
     </row>
@@ -33067,7 +33054,7 @@
       <c r="B42" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="30" t="s">
         <v>433</v>
       </c>
     </row>
@@ -33078,7 +33065,7 @@
       <c r="B43" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="30" t="s">
         <v>434</v>
       </c>
     </row>
@@ -33089,7 +33076,7 @@
       <c r="B44" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="30" t="s">
         <v>435</v>
       </c>
     </row>
@@ -33100,7 +33087,7 @@
       <c r="B45" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="30" t="s">
         <v>436</v>
       </c>
     </row>
@@ -33111,7 +33098,7 @@
       <c r="B46" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="30" t="s">
         <v>437</v>
       </c>
     </row>
@@ -33122,7 +33109,7 @@
       <c r="B47" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="30" t="s">
         <v>438</v>
       </c>
     </row>
@@ -33133,7 +33120,7 @@
       <c r="B48" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="35" t="s">
+      <c r="D48" s="30" t="s">
         <v>439</v>
       </c>
     </row>
@@ -33144,7 +33131,7 @@
       <c r="B49" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D49" s="30" t="s">
         <v>440</v>
       </c>
     </row>
@@ -33155,7 +33142,7 @@
       <c r="B50" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D50" s="35" t="s">
+      <c r="D50" s="30" t="s">
         <v>441</v>
       </c>
     </row>
@@ -33166,7 +33153,7 @@
       <c r="B51" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="35" t="s">
+      <c r="D51" s="30" t="s">
         <v>442</v>
       </c>
     </row>
@@ -33177,7 +33164,7 @@
       <c r="B52" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="35" t="s">
+      <c r="D52" s="30" t="s">
         <v>443</v>
       </c>
     </row>
@@ -33188,7 +33175,7 @@
       <c r="B53" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D53" s="35" t="s">
+      <c r="D53" s="30" t="s">
         <v>444</v>
       </c>
     </row>
@@ -33199,7 +33186,7 @@
       <c r="B54" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D54" s="36" t="s">
+      <c r="D54" s="31" t="s">
         <v>445</v>
       </c>
     </row>
@@ -33210,7 +33197,7 @@
       <c r="B55" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="36" t="s">
+      <c r="D55" s="31" t="s">
         <v>446</v>
       </c>
     </row>
@@ -33221,7 +33208,7 @@
       <c r="B56" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="36" t="s">
+      <c r="D56" s="31" t="s">
         <v>447</v>
       </c>
     </row>
@@ -33232,7 +33219,7 @@
       <c r="B57" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="30" t="s">
         <v>448</v>
       </c>
     </row>
@@ -33243,7 +33230,7 @@
       <c r="B58" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="30" t="s">
         <v>449</v>
       </c>
     </row>
@@ -33254,7 +33241,7 @@
       <c r="B59" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D59" s="36" t="s">
+      <c r="D59" s="31" t="s">
         <v>450</v>
       </c>
     </row>
@@ -33265,7 +33252,7 @@
       <c r="B60" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D60" s="35" t="s">
+      <c r="D60" s="30" t="s">
         <v>451</v>
       </c>
     </row>
@@ -33276,7 +33263,7 @@
       <c r="B61" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="35" t="s">
+      <c r="D61" s="30" t="s">
         <v>452</v>
       </c>
     </row>
@@ -33287,7 +33274,7 @@
       <c r="B62" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D62" s="35" t="s">
+      <c r="D62" s="30" t="s">
         <v>453</v>
       </c>
     </row>
@@ -33298,7 +33285,7 @@
       <c r="B63" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D63" s="35" t="s">
+      <c r="D63" s="30" t="s">
         <v>454</v>
       </c>
     </row>
@@ -33309,7 +33296,7 @@
       <c r="B64" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D64" s="35" t="s">
+      <c r="D64" s="30" t="s">
         <v>455</v>
       </c>
     </row>
@@ -33320,7 +33307,7 @@
       <c r="B65" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D65" s="35" t="s">
+      <c r="D65" s="30" t="s">
         <v>456</v>
       </c>
     </row>
@@ -33331,7 +33318,7 @@
       <c r="B66" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D66" s="35" t="s">
+      <c r="D66" s="30" t="s">
         <v>457</v>
       </c>
     </row>
@@ -33342,7 +33329,7 @@
       <c r="B67" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D67" s="36" t="s">
+      <c r="D67" s="31" t="s">
         <v>458</v>
       </c>
     </row>
@@ -33353,7 +33340,7 @@
       <c r="B68" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D68" s="36" t="s">
+      <c r="D68" s="31" t="s">
         <v>459</v>
       </c>
     </row>
@@ -33364,7 +33351,7 @@
       <c r="B69" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="35" t="s">
+      <c r="D69" s="30" t="s">
         <v>460</v>
       </c>
     </row>
@@ -33375,7 +33362,7 @@
       <c r="B70" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D70" s="36" t="s">
+      <c r="D70" s="31" t="s">
         <v>461</v>
       </c>
     </row>
@@ -33386,7 +33373,7 @@
       <c r="B71" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D71" s="35" t="s">
+      <c r="D71" s="30" t="s">
         <v>462</v>
       </c>
     </row>
@@ -33397,7 +33384,7 @@
       <c r="B72" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D72" s="35" t="s">
+      <c r="D72" s="30" t="s">
         <v>463</v>
       </c>
     </row>
@@ -33408,7 +33395,7 @@
       <c r="B73" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="35" t="s">
+      <c r="D73" s="30" t="s">
         <v>464</v>
       </c>
     </row>
@@ -33419,7 +33406,7 @@
       <c r="B74" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D74" s="35" t="s">
+      <c r="D74" s="30" t="s">
         <v>465</v>
       </c>
     </row>
@@ -33430,7 +33417,7 @@
       <c r="B75" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D75" s="35" t="s">
+      <c r="D75" s="30" t="s">
         <v>466</v>
       </c>
     </row>
@@ -33441,7 +33428,7 @@
       <c r="B76" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D76" s="35" t="s">
+      <c r="D76" s="30" t="s">
         <v>467</v>
       </c>
     </row>
@@ -33452,7 +33439,7 @@
       <c r="B77" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D77" s="35" t="s">
+      <c r="D77" s="30" t="s">
         <v>468</v>
       </c>
     </row>
@@ -33463,7 +33450,7 @@
       <c r="B78" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D78" s="35" t="s">
+      <c r="D78" s="30" t="s">
         <v>469</v>
       </c>
     </row>
@@ -33474,7 +33461,7 @@
       <c r="B79" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D79" s="35" t="s">
+      <c r="D79" s="30" t="s">
         <v>470</v>
       </c>
     </row>
@@ -33485,7 +33472,7 @@
       <c r="B80" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D80" s="35" t="s">
+      <c r="D80" s="30" t="s">
         <v>471</v>
       </c>
     </row>
@@ -33496,7 +33483,7 @@
       <c r="B81" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D81" s="35" t="s">
+      <c r="D81" s="30" t="s">
         <v>472</v>
       </c>
     </row>
@@ -33507,7 +33494,7 @@
       <c r="B82" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D82" s="36" t="s">
+      <c r="D82" s="31" t="s">
         <v>473</v>
       </c>
     </row>
@@ -33518,7 +33505,7 @@
       <c r="B83" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D83" s="35" t="s">
+      <c r="D83" s="30" t="s">
         <v>474</v>
       </c>
     </row>
@@ -33529,7 +33516,7 @@
       <c r="B84" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D84" s="35" t="s">
+      <c r="D84" s="30" t="s">
         <v>475</v>
       </c>
     </row>
@@ -33540,7 +33527,7 @@
       <c r="B85" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D85" s="35" t="s">
+      <c r="D85" s="30" t="s">
         <v>476</v>
       </c>
     </row>
@@ -33551,7 +33538,7 @@
       <c r="B86" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="D86" s="36" t="s">
+      <c r="D86" s="31" t="s">
         <v>477</v>
       </c>
     </row>
@@ -33562,7 +33549,7 @@
       <c r="B87" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="35" t="s">
+      <c r="D87" s="30" t="s">
         <v>478</v>
       </c>
     </row>
@@ -33573,7 +33560,7 @@
       <c r="B88" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D88" s="35" t="s">
+      <c r="D88" s="30" t="s">
         <v>479</v>
       </c>
     </row>
@@ -33584,7 +33571,7 @@
       <c r="B89" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D89" s="35" t="s">
+      <c r="D89" s="30" t="s">
         <v>480</v>
       </c>
     </row>
@@ -33595,7 +33582,7 @@
       <c r="B90" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="D90" s="35" t="s">
+      <c r="D90" s="30" t="s">
         <v>481</v>
       </c>
     </row>
@@ -33606,7 +33593,7 @@
       <c r="B91" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D91" s="35" t="s">
+      <c r="D91" s="30" t="s">
         <v>482</v>
       </c>
     </row>
@@ -33617,7 +33604,7 @@
       <c r="B92" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D92" s="35" t="s">
+      <c r="D92" s="30" t="s">
         <v>483</v>
       </c>
     </row>
@@ -33628,7 +33615,7 @@
       <c r="B93" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="D93" s="35" t="s">
+      <c r="D93" s="30" t="s">
         <v>484</v>
       </c>
     </row>
@@ -33639,7 +33626,7 @@
       <c r="B94" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="D94" s="35" t="s">
+      <c r="D94" s="30" t="s">
         <v>485</v>
       </c>
     </row>
@@ -33650,7 +33637,7 @@
       <c r="B95" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D95" s="35" t="s">
+      <c r="D95" s="30" t="s">
         <v>486</v>
       </c>
     </row>
@@ -33661,7 +33648,7 @@
       <c r="B96" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="D96" s="36" t="s">
+      <c r="D96" s="31" t="s">
         <v>487</v>
       </c>
     </row>
@@ -33672,7 +33659,7 @@
       <c r="B97" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="D97" s="35" t="s">
+      <c r="D97" s="30" t="s">
         <v>488</v>
       </c>
     </row>
@@ -33683,7 +33670,7 @@
       <c r="B98" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="D98" s="35" t="s">
+      <c r="D98" s="30" t="s">
         <v>489</v>
       </c>
     </row>
@@ -33694,7 +33681,7 @@
       <c r="B99" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D99" s="35" t="s">
+      <c r="D99" s="30" t="s">
         <v>490</v>
       </c>
     </row>
@@ -33705,7 +33692,7 @@
       <c r="B100" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="D100" s="35" t="s">
+      <c r="D100" s="30" t="s">
         <v>491</v>
       </c>
     </row>
@@ -33716,7 +33703,7 @@
       <c r="B101" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="D101" s="35" t="s">
+      <c r="D101" s="30" t="s">
         <v>492</v>
       </c>
     </row>
@@ -33727,7 +33714,7 @@
       <c r="B102" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="35" t="s">
+      <c r="D102" s="30" t="s">
         <v>493</v>
       </c>
     </row>
@@ -33738,7 +33725,7 @@
       <c r="B103" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D103" s="35" t="s">
+      <c r="D103" s="30" t="s">
         <v>494</v>
       </c>
     </row>
@@ -33749,7 +33736,7 @@
       <c r="B104" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D104" s="35" t="s">
+      <c r="D104" s="30" t="s">
         <v>495</v>
       </c>
     </row>
@@ -33760,7 +33747,7 @@
       <c r="B105" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D105" s="36" t="s">
+      <c r="D105" s="31" t="s">
         <v>496</v>
       </c>
     </row>
@@ -33771,7 +33758,7 @@
       <c r="B106" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="D106" s="36" t="s">
+      <c r="D106" s="31" t="s">
         <v>497</v>
       </c>
     </row>
@@ -33782,7 +33769,7 @@
       <c r="B107" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D107" s="35" t="s">
+      <c r="D107" s="30" t="s">
         <v>498</v>
       </c>
     </row>
@@ -33793,7 +33780,7 @@
       <c r="B108" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="D108" s="31" t="s">
+      <c r="D108" s="28" t="s">
         <v>499</v>
       </c>
     </row>
@@ -33804,7 +33791,7 @@
       <c r="B109" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D109" s="37" t="s">
+      <c r="D109" s="32" t="s">
         <v>500</v>
       </c>
     </row>
@@ -33815,7 +33802,7 @@
       <c r="B110" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="D110" s="31" t="s">
+      <c r="D110" s="28" t="s">
         <v>501</v>
       </c>
     </row>
@@ -33826,7 +33813,7 @@
       <c r="B111" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D111" s="31" t="s">
+      <c r="D111" s="28" t="s">
         <v>502</v>
       </c>
     </row>
@@ -33837,7 +33824,7 @@
       <c r="B112" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D112" s="35" t="s">
+      <c r="D112" s="30" t="s">
         <v>503</v>
       </c>
     </row>
@@ -34333,12 +34320,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
